--- a/artfynd/A 24249-2024 artfynd.xlsx
+++ b/artfynd/A 24249-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>118676083</v>
       </c>
       <c r="B2" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 24249-2024 artfynd.xlsx
+++ b/artfynd/A 24249-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124324981</v>
+        <v>124324530</v>
       </c>
       <c r="B3" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490817</v>
+        <v>490855</v>
       </c>
       <c r="R3" t="n">
-        <v>6865147</v>
+        <v>6864955</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -888,7 +888,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124323613</v>
+        <v>124323622</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -928,13 +928,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490844</v>
+        <v>490832</v>
       </c>
       <c r="R4" t="n">
-        <v>6865014</v>
+        <v>6865017</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,19 +978,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124324272</v>
+        <v>124323908</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1030,13 +1030,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490869</v>
+        <v>490844</v>
       </c>
       <c r="R5" t="n">
-        <v>6864990</v>
+        <v>6864975</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,19 +1080,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124324899</v>
+        <v>124324301</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490800</v>
+        <v>490835</v>
       </c>
       <c r="R6" t="n">
-        <v>6865161</v>
+        <v>6864998</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,19 +1182,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124324301</v>
+        <v>124324110</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1234,13 +1234,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490835</v>
+        <v>490853</v>
       </c>
       <c r="R7" t="n">
-        <v>6864998</v>
+        <v>6865011</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1284,19 +1284,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124323622</v>
+        <v>124323575</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1336,13 +1336,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490832</v>
+        <v>490851</v>
       </c>
       <c r="R8" t="n">
-        <v>6865017</v>
+        <v>6865050</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124323707</v>
+        <v>124324981</v>
       </c>
       <c r="B10" t="n">
         <v>79892</v>
@@ -1540,13 +1540,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490838</v>
+        <v>490817</v>
       </c>
       <c r="R10" t="n">
-        <v>6865007</v>
+        <v>6865147</v>
       </c>
       <c r="S10" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1590,22 +1590,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124324167</v>
+        <v>124323707</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1618,21 +1618,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1642,13 +1642,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490860</v>
+        <v>490838</v>
       </c>
       <c r="R11" t="n">
-        <v>6864997</v>
+        <v>6865007</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1692,22 +1692,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124324393</v>
+        <v>124324899</v>
       </c>
       <c r="B12" t="n">
-        <v>78889</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1720,21 +1720,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1744,13 +1744,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490851</v>
+        <v>490800</v>
       </c>
       <c r="R12" t="n">
-        <v>6864963</v>
+        <v>6865161</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124324110</v>
+        <v>124325022</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -1846,13 +1846,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490853</v>
+        <v>490825</v>
       </c>
       <c r="R13" t="n">
-        <v>6865011</v>
+        <v>6865147</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124323891</v>
+        <v>124324272</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1924,21 +1924,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1948,13 +1948,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490832</v>
+        <v>490869</v>
       </c>
       <c r="R14" t="n">
-        <v>6865023</v>
+        <v>6864990</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1984,11 +1984,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-22</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2015,7 +2010,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124323575</v>
+        <v>124323587</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2055,13 +2050,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490851</v>
+        <v>490850</v>
       </c>
       <c r="R15" t="n">
-        <v>6865050</v>
+        <v>6865018</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2105,22 +2100,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124323716</v>
+        <v>124325068</v>
       </c>
       <c r="B16" t="n">
-        <v>79891</v>
+        <v>56722</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2129,25 +2124,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2157,13 +2152,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490841</v>
+        <v>490832</v>
       </c>
       <c r="R16" t="n">
-        <v>6865011</v>
+        <v>6865135</v>
       </c>
       <c r="S16" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2193,6 +2188,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2207,22 +2207,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124325068</v>
+        <v>124324192</v>
       </c>
       <c r="B17" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2231,25 +2231,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490832</v>
+        <v>490878</v>
       </c>
       <c r="R17" t="n">
-        <v>6865135</v>
+        <v>6864994</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2295,11 +2295,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-22</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2326,10 +2321,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124324192</v>
+        <v>124323858</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>91579</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2338,41 +2333,50 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490878</v>
+        <v>490832</v>
       </c>
       <c r="R18" t="n">
-        <v>6864994</v>
+        <v>6865023</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2416,22 +2420,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124323908</v>
+        <v>124323891</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2444,21 +2448,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2468,13 +2472,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490844</v>
+        <v>490832</v>
       </c>
       <c r="R19" t="n">
-        <v>6864975</v>
+        <v>6865023</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2504,6 +2508,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2518,19 +2527,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124324530</v>
+        <v>124323613</v>
       </c>
       <c r="B20" t="n">
         <v>78810</v>
@@ -2566,14 +2575,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490855</v>
+        <v>490844</v>
       </c>
       <c r="R20" t="n">
-        <v>6864955</v>
+        <v>6865014</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2632,10 +2641,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124325022</v>
+        <v>124323716</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2648,21 +2657,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2672,13 +2681,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490825</v>
+        <v>490841</v>
       </c>
       <c r="R21" t="n">
-        <v>6865147</v>
+        <v>6865011</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2722,22 +2731,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124323858</v>
+        <v>124323971</v>
       </c>
       <c r="B22" t="n">
-        <v>91579</v>
+        <v>78546</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2746,50 +2755,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>760</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490832</v>
+        <v>490853</v>
       </c>
       <c r="R22" t="n">
-        <v>6865023</v>
+        <v>6865017</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2833,19 +2833,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124323587</v>
+        <v>124324167</v>
       </c>
       <c r="B23" t="n">
         <v>78810</v>
@@ -2881,14 +2881,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490850</v>
+        <v>490860</v>
       </c>
       <c r="R23" t="n">
-        <v>6865018</v>
+        <v>6864997</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2947,10 +2947,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124323971</v>
+        <v>124324393</v>
       </c>
       <c r="B24" t="n">
-        <v>78546</v>
+        <v>78889</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2963,21 +2963,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>864</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490853</v>
+        <v>490851</v>
       </c>
       <c r="R24" t="n">
-        <v>6865017</v>
+        <v>6864963</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3049,7 +3049,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124364538</v>
+        <v>124365978</v>
       </c>
       <c r="B25" t="n">
         <v>78810</v>
@@ -3085,14 +3085,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullberget, Kullberget, Hls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491166</v>
+        <v>490934</v>
       </c>
       <c r="R25" t="n">
-        <v>6865362</v>
+        <v>6865221</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3122,9 +3122,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3139,19 +3149,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124365822</v>
+        <v>124364810</v>
       </c>
       <c r="B26" t="n">
         <v>78810</v>
@@ -3191,10 +3201,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490796</v>
+        <v>491146</v>
       </c>
       <c r="R26" t="n">
-        <v>6865155</v>
+        <v>6865207</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3253,10 +3263,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124365787</v>
+        <v>124364538</v>
       </c>
       <c r="B27" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3269,37 +3279,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490822</v>
+        <v>491166</v>
       </c>
       <c r="R27" t="n">
-        <v>6865151</v>
+        <v>6865362</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3355,7 +3365,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124365903</v>
+        <v>124365822</v>
       </c>
       <c r="B28" t="n">
         <v>78810</v>
@@ -3395,10 +3405,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490934</v>
+        <v>490796</v>
       </c>
       <c r="R28" t="n">
-        <v>6865221</v>
+        <v>6865155</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3428,19 +3438,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>16:02</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>16:02</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3455,22 +3455,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124365478</v>
+        <v>124365787</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3483,21 +3483,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490807</v>
+        <v>490822</v>
       </c>
       <c r="R29" t="n">
-        <v>6865148</v>
+        <v>6865151</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124364810</v>
+        <v>124365478</v>
       </c>
       <c r="B30" t="n">
         <v>78810</v>
@@ -3609,10 +3609,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>491146</v>
+        <v>490807</v>
       </c>
       <c r="R30" t="n">
-        <v>6865207</v>
+        <v>6865148</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3671,7 +3671,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124364496</v>
+        <v>124364652</v>
       </c>
       <c r="B31" t="n">
         <v>78810</v>
@@ -3711,13 +3711,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>491193</v>
+        <v>491120</v>
       </c>
       <c r="R31" t="n">
-        <v>6865330</v>
+        <v>6865386</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124364652</v>
+        <v>124364496</v>
       </c>
       <c r="B33" t="n">
         <v>78810</v>
@@ -3915,13 +3915,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>491120</v>
+        <v>491193</v>
       </c>
       <c r="R33" t="n">
-        <v>6865386</v>
+        <v>6865330</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>

--- a/artfynd/A 24249-2024 artfynd.xlsx
+++ b/artfynd/A 24249-2024 artfynd.xlsx
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124324530</v>
+        <v>124325022</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -826,13 +826,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490855</v>
+        <v>490825</v>
       </c>
       <c r="R3" t="n">
-        <v>6864955</v>
+        <v>6865147</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124323622</v>
+        <v>124323858</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>91579</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,41 +900,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>490832</v>
       </c>
       <c r="R4" t="n">
-        <v>6865017</v>
+        <v>6865023</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124323908</v>
+        <v>124323971</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,21 +1015,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,13 +1039,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490844</v>
+        <v>490853</v>
       </c>
       <c r="R5" t="n">
-        <v>6864975</v>
+        <v>6865017</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,19 +1089,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124324301</v>
+        <v>124324167</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1132,13 +1141,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490835</v>
+        <v>490860</v>
       </c>
       <c r="R6" t="n">
-        <v>6864998</v>
+        <v>6864997</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1182,19 +1191,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124324110</v>
+        <v>124324301</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1234,13 +1243,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490853</v>
+        <v>490835</v>
       </c>
       <c r="R7" t="n">
-        <v>6865011</v>
+        <v>6864998</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1284,19 +1293,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124323575</v>
+        <v>124324272</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1332,17 +1341,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490851</v>
+        <v>490869</v>
       </c>
       <c r="R8" t="n">
-        <v>6865050</v>
+        <v>6864990</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1386,22 +1395,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124324335</v>
+        <v>124323707</v>
       </c>
       <c r="B9" t="n">
-        <v>74901</v>
+        <v>79892</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1414,21 +1423,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1438,13 +1447,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490869</v>
+        <v>490838</v>
       </c>
       <c r="R9" t="n">
-        <v>6864990</v>
+        <v>6865007</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1488,22 +1497,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124324981</v>
+        <v>124323575</v>
       </c>
       <c r="B10" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1516,37 +1525,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490817</v>
+        <v>490851</v>
       </c>
       <c r="R10" t="n">
-        <v>6865147</v>
+        <v>6865050</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1590,22 +1599,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124323707</v>
+        <v>124323622</v>
       </c>
       <c r="B11" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1618,37 +1627,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490838</v>
+        <v>490832</v>
       </c>
       <c r="R11" t="n">
-        <v>6865007</v>
+        <v>6865017</v>
       </c>
       <c r="S11" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1704,7 +1713,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124324899</v>
+        <v>124323587</v>
       </c>
       <c r="B12" t="n">
         <v>78810</v>
@@ -1740,17 +1749,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490800</v>
+        <v>490850</v>
       </c>
       <c r="R12" t="n">
-        <v>6865161</v>
+        <v>6865018</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1806,7 +1815,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124325022</v>
+        <v>124323613</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -1842,17 +1851,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490825</v>
+        <v>490844</v>
       </c>
       <c r="R13" t="n">
-        <v>6865147</v>
+        <v>6865014</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1908,7 +1917,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124324272</v>
+        <v>124324530</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -1948,10 +1957,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490869</v>
+        <v>490855</v>
       </c>
       <c r="R14" t="n">
-        <v>6864990</v>
+        <v>6864955</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2010,7 +2019,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124323587</v>
+        <v>124323908</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2046,17 +2055,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490850</v>
+        <v>490844</v>
       </c>
       <c r="R15" t="n">
-        <v>6865018</v>
+        <v>6864975</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2100,22 +2109,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124325068</v>
+        <v>124324335</v>
       </c>
       <c r="B16" t="n">
-        <v>56722</v>
+        <v>74901</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2124,25 +2133,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2152,10 +2161,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490832</v>
+        <v>490869</v>
       </c>
       <c r="R16" t="n">
-        <v>6865135</v>
+        <v>6864990</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2188,11 +2197,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-22</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2321,10 +2325,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124323858</v>
+        <v>124324899</v>
       </c>
       <c r="B18" t="n">
-        <v>91579</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2333,50 +2337,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490832</v>
+        <v>490800</v>
       </c>
       <c r="R18" t="n">
-        <v>6865023</v>
+        <v>6865161</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2420,22 +2415,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124323891</v>
+        <v>124324981</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>79892</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2448,21 +2443,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2472,13 +2467,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490832</v>
+        <v>490817</v>
       </c>
       <c r="R19" t="n">
-        <v>6865023</v>
+        <v>6865147</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2508,11 +2503,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-22</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2539,7 +2529,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124323613</v>
+        <v>124324110</v>
       </c>
       <c r="B20" t="n">
         <v>78810</v>
@@ -2575,14 +2565,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490844</v>
+        <v>490853</v>
       </c>
       <c r="R20" t="n">
-        <v>6865014</v>
+        <v>6865011</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2641,10 +2631,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124323716</v>
+        <v>124324393</v>
       </c>
       <c r="B21" t="n">
-        <v>79891</v>
+        <v>78889</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2657,21 +2647,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>864</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2681,13 +2671,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490841</v>
+        <v>490851</v>
       </c>
       <c r="R21" t="n">
-        <v>6865011</v>
+        <v>6864963</v>
       </c>
       <c r="S21" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2731,22 +2721,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124323971</v>
+        <v>124323891</v>
       </c>
       <c r="B22" t="n">
-        <v>78546</v>
+        <v>57513</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2759,21 +2749,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2783,13 +2773,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490853</v>
+        <v>490832</v>
       </c>
       <c r="R22" t="n">
-        <v>6865017</v>
+        <v>6865023</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2819,6 +2809,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2845,10 +2840,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124324167</v>
+        <v>124323716</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2861,21 +2856,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2885,13 +2880,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490860</v>
+        <v>490841</v>
       </c>
       <c r="R23" t="n">
-        <v>6864997</v>
+        <v>6865011</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2935,22 +2930,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124324393</v>
+        <v>124325068</v>
       </c>
       <c r="B24" t="n">
-        <v>78889</v>
+        <v>56722</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2959,25 +2954,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>864</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2987,10 +2982,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490851</v>
+        <v>490832</v>
       </c>
       <c r="R24" t="n">
-        <v>6864963</v>
+        <v>6865135</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3023,6 +3018,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3049,10 +3049,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124365978</v>
+        <v>124365787</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3065,37 +3065,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kullberget, Kullberget, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490934</v>
+        <v>490822</v>
       </c>
       <c r="R25" t="n">
-        <v>6865221</v>
+        <v>6865151</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3122,19 +3122,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>16:07</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3149,19 +3139,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124364810</v>
+        <v>124365822</v>
       </c>
       <c r="B26" t="n">
         <v>78810</v>
@@ -3201,10 +3191,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>491146</v>
+        <v>490796</v>
       </c>
       <c r="R26" t="n">
-        <v>6865207</v>
+        <v>6865155</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3263,7 +3253,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124364538</v>
+        <v>124364810</v>
       </c>
       <c r="B27" t="n">
         <v>78810</v>
@@ -3299,14 +3289,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491166</v>
+        <v>491146</v>
       </c>
       <c r="R27" t="n">
-        <v>6865362</v>
+        <v>6865207</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3365,7 +3355,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124365822</v>
+        <v>124364652</v>
       </c>
       <c r="B28" t="n">
         <v>78810</v>
@@ -3401,17 +3391,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490796</v>
+        <v>491120</v>
       </c>
       <c r="R28" t="n">
-        <v>6865155</v>
+        <v>6865386</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3467,10 +3457,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124365787</v>
+        <v>124365903</v>
       </c>
       <c r="B29" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3483,21 +3473,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3507,13 +3497,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490822</v>
+        <v>490934</v>
       </c>
       <c r="R29" t="n">
-        <v>6865151</v>
+        <v>6865221</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3540,9 +3530,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3557,12 +3557,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3671,7 +3671,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124364652</v>
+        <v>124365206</v>
       </c>
       <c r="B31" t="n">
         <v>78810</v>
@@ -3707,17 +3707,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>491120</v>
+        <v>491179</v>
       </c>
       <c r="R31" t="n">
-        <v>6865386</v>
+        <v>6865114</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124365206</v>
+        <v>124364496</v>
       </c>
       <c r="B32" t="n">
         <v>78810</v>
@@ -3809,14 +3809,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>491179</v>
+        <v>491193</v>
       </c>
       <c r="R32" t="n">
-        <v>6865114</v>
+        <v>6865330</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3875,7 +3875,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124364496</v>
+        <v>124364538</v>
       </c>
       <c r="B33" t="n">
         <v>78810</v>
@@ -3915,10 +3915,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>491193</v>
+        <v>491166</v>
       </c>
       <c r="R33" t="n">
-        <v>6865330</v>
+        <v>6865362</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>

--- a/artfynd/A 24249-2024 artfynd.xlsx
+++ b/artfynd/A 24249-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124325022</v>
+        <v>124325068</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,13 +826,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490825</v>
+        <v>490832</v>
       </c>
       <c r="R3" t="n">
-        <v>6865147</v>
+        <v>6865135</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,6 +862,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124323858</v>
+        <v>124323971</v>
       </c>
       <c r="B4" t="n">
-        <v>91579</v>
+        <v>78546</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,50 +905,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>760</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490832</v>
+        <v>490853</v>
       </c>
       <c r="R4" t="n">
-        <v>6865023</v>
+        <v>6865017</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,22 +983,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124323971</v>
+        <v>124325022</v>
       </c>
       <c r="B5" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,21 +1011,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,13 +1035,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490853</v>
+        <v>490825</v>
       </c>
       <c r="R5" t="n">
-        <v>6865017</v>
+        <v>6865147</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,7 +1097,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124324167</v>
+        <v>124323622</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1137,17 +1133,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490860</v>
+        <v>490832</v>
       </c>
       <c r="R6" t="n">
-        <v>6864997</v>
+        <v>6865017</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1191,22 +1187,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124324301</v>
+        <v>124323707</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1219,21 +1215,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1243,13 +1239,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490835</v>
+        <v>490838</v>
       </c>
       <c r="R7" t="n">
-        <v>6864998</v>
+        <v>6865007</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,7 +1301,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124324272</v>
+        <v>124324192</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1345,10 +1341,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490869</v>
+        <v>490878</v>
       </c>
       <c r="R8" t="n">
-        <v>6864990</v>
+        <v>6864994</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1407,10 +1403,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124323707</v>
+        <v>124323891</v>
       </c>
       <c r="B9" t="n">
-        <v>79892</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1423,21 +1419,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1447,13 +1443,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490838</v>
+        <v>490832</v>
       </c>
       <c r="R9" t="n">
-        <v>6865007</v>
+        <v>6865023</v>
       </c>
       <c r="S9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1483,6 +1479,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1497,12 +1498,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1611,7 +1612,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124323622</v>
+        <v>124324272</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1647,17 +1648,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490832</v>
+        <v>490869</v>
       </c>
       <c r="R11" t="n">
-        <v>6865017</v>
+        <v>6864990</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1701,19 +1702,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124323587</v>
+        <v>124323908</v>
       </c>
       <c r="B12" t="n">
         <v>78810</v>
@@ -1749,17 +1750,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490850</v>
+        <v>490844</v>
       </c>
       <c r="R12" t="n">
-        <v>6865018</v>
+        <v>6864975</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1803,22 +1804,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124323613</v>
+        <v>124324335</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1831,34 +1832,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490844</v>
+        <v>490869</v>
       </c>
       <c r="R13" t="n">
-        <v>6865014</v>
+        <v>6864990</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1917,7 +1918,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124324530</v>
+        <v>124324167</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -1957,10 +1958,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490855</v>
+        <v>490860</v>
       </c>
       <c r="R14" t="n">
-        <v>6864955</v>
+        <v>6864997</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2019,10 +2020,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124323908</v>
+        <v>124324981</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2035,21 +2036,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2059,13 +2060,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490844</v>
+        <v>490817</v>
       </c>
       <c r="R15" t="n">
-        <v>6864975</v>
+        <v>6865147</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2109,22 +2110,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124324335</v>
+        <v>124323587</v>
       </c>
       <c r="B16" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2137,34 +2138,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490869</v>
+        <v>490850</v>
       </c>
       <c r="R16" t="n">
-        <v>6864990</v>
+        <v>6865018</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2223,7 +2224,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124324192</v>
+        <v>124324899</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2263,13 +2264,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490878</v>
+        <v>490800</v>
       </c>
       <c r="R17" t="n">
-        <v>6864994</v>
+        <v>6865161</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2325,7 +2326,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124324899</v>
+        <v>124324301</v>
       </c>
       <c r="B18" t="n">
         <v>78810</v>
@@ -2365,10 +2366,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490800</v>
+        <v>490835</v>
       </c>
       <c r="R18" t="n">
-        <v>6865161</v>
+        <v>6864998</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2415,22 +2416,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124324981</v>
+        <v>124323613</v>
       </c>
       <c r="B19" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2443,34 +2444,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490817</v>
+        <v>490844</v>
       </c>
       <c r="R19" t="n">
-        <v>6865147</v>
+        <v>6865014</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2529,10 +2530,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124324110</v>
+        <v>124323716</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2545,21 +2546,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2569,13 +2570,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490853</v>
+        <v>490841</v>
       </c>
       <c r="R20" t="n">
         <v>6865011</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2619,12 +2620,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2733,10 +2734,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124323891</v>
+        <v>124324110</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2749,21 +2750,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2773,13 +2774,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490832</v>
+        <v>490853</v>
       </c>
       <c r="R22" t="n">
-        <v>6865023</v>
+        <v>6865011</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2809,11 +2810,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-22</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2840,10 +2836,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124323716</v>
+        <v>124323858</v>
       </c>
       <c r="B23" t="n">
-        <v>79891</v>
+        <v>91579</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2852,41 +2848,50 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490841</v>
+        <v>490832</v>
       </c>
       <c r="R23" t="n">
-        <v>6865011</v>
+        <v>6865023</v>
       </c>
       <c r="S23" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2942,10 +2947,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124325068</v>
+        <v>124324530</v>
       </c>
       <c r="B24" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2954,25 +2959,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2982,10 +2987,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490832</v>
+        <v>490855</v>
       </c>
       <c r="R24" t="n">
-        <v>6865135</v>
+        <v>6864955</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3018,11 +3023,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-22</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3049,10 +3049,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124365787</v>
+        <v>124364810</v>
       </c>
       <c r="B25" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3065,21 +3065,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3089,13 +3089,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490822</v>
+        <v>491146</v>
       </c>
       <c r="R25" t="n">
-        <v>6865151</v>
+        <v>6865207</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124365822</v>
+        <v>124365978</v>
       </c>
       <c r="B26" t="n">
         <v>78810</v>
@@ -3187,14 +3187,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Kullberget, Kullberget, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490796</v>
+        <v>490934</v>
       </c>
       <c r="R26" t="n">
-        <v>6865155</v>
+        <v>6865221</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3224,9 +3224,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3241,19 +3251,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124364810</v>
+        <v>124365822</v>
       </c>
       <c r="B27" t="n">
         <v>78810</v>
@@ -3293,10 +3303,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491146</v>
+        <v>490796</v>
       </c>
       <c r="R27" t="n">
-        <v>6865207</v>
+        <v>6865155</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3355,7 +3365,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124364652</v>
+        <v>124364538</v>
       </c>
       <c r="B28" t="n">
         <v>78810</v>
@@ -3395,13 +3405,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>491120</v>
+        <v>491166</v>
       </c>
       <c r="R28" t="n">
-        <v>6865386</v>
+        <v>6865362</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3457,7 +3467,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124365903</v>
+        <v>124365206</v>
       </c>
       <c r="B29" t="n">
         <v>78810</v>
@@ -3497,10 +3507,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490934</v>
+        <v>491179</v>
       </c>
       <c r="R29" t="n">
-        <v>6865221</v>
+        <v>6865114</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3530,19 +3540,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>16:02</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>16:02</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3557,22 +3557,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124365478</v>
+        <v>124365787</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3585,21 +3585,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3609,13 +3609,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490807</v>
+        <v>490822</v>
       </c>
       <c r="R30" t="n">
-        <v>6865148</v>
+        <v>6865151</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124365206</v>
+        <v>124365478</v>
       </c>
       <c r="B31" t="n">
         <v>78810</v>
@@ -3711,10 +3711,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>491179</v>
+        <v>490807</v>
       </c>
       <c r="R31" t="n">
-        <v>6865114</v>
+        <v>6865148</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3773,7 +3773,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124364496</v>
+        <v>124364652</v>
       </c>
       <c r="B32" t="n">
         <v>78810</v>
@@ -3813,13 +3813,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>491193</v>
+        <v>491120</v>
       </c>
       <c r="R32" t="n">
-        <v>6865330</v>
+        <v>6865386</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124364538</v>
+        <v>124364496</v>
       </c>
       <c r="B33" t="n">
         <v>78810</v>
@@ -3915,10 +3915,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>491166</v>
+        <v>491193</v>
       </c>
       <c r="R33" t="n">
-        <v>6865362</v>
+        <v>6865330</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>

--- a/artfynd/A 24249-2024 artfynd.xlsx
+++ b/artfynd/A 24249-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124325068</v>
+        <v>124324301</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,13 +826,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490832</v>
+        <v>490835</v>
       </c>
       <c r="R3" t="n">
-        <v>6865135</v>
+        <v>6864998</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,11 +862,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-22</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,22 +876,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124323971</v>
+        <v>124324981</v>
       </c>
       <c r="B4" t="n">
-        <v>78546</v>
+        <v>79892</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,21 +904,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -933,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490853</v>
+        <v>490817</v>
       </c>
       <c r="R4" t="n">
-        <v>6865017</v>
+        <v>6865147</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -995,7 +990,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124325022</v>
+        <v>124324530</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1035,13 +1030,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490825</v>
+        <v>490855</v>
       </c>
       <c r="R5" t="n">
-        <v>6865147</v>
+        <v>6864955</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1097,7 +1092,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124323622</v>
+        <v>124324110</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1133,17 +1128,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490832</v>
+        <v>490853</v>
       </c>
       <c r="R6" t="n">
-        <v>6865017</v>
+        <v>6865011</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1187,22 +1182,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124323707</v>
+        <v>124323891</v>
       </c>
       <c r="B7" t="n">
-        <v>79892</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1215,21 +1210,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1239,13 +1234,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490838</v>
+        <v>490832</v>
       </c>
       <c r="R7" t="n">
-        <v>6865007</v>
+        <v>6865023</v>
       </c>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1275,6 +1270,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1289,22 +1289,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124324192</v>
+        <v>124324335</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1317,21 +1317,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490878</v>
+        <v>490869</v>
       </c>
       <c r="R8" t="n">
-        <v>6864994</v>
+        <v>6864990</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1403,10 +1403,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124323891</v>
+        <v>124323716</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1419,21 +1419,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490832</v>
+        <v>490841</v>
       </c>
       <c r="R9" t="n">
-        <v>6865023</v>
+        <v>6865011</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1479,11 +1479,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-22</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1498,19 +1493,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124323575</v>
+        <v>124324192</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1546,17 +1541,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490851</v>
+        <v>490878</v>
       </c>
       <c r="R10" t="n">
-        <v>6865050</v>
+        <v>6864994</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1600,19 +1595,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124324272</v>
+        <v>124324899</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1652,13 +1647,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490869</v>
+        <v>490800</v>
       </c>
       <c r="R11" t="n">
-        <v>6864990</v>
+        <v>6865161</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1714,7 +1709,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124323908</v>
+        <v>124324167</v>
       </c>
       <c r="B12" t="n">
         <v>78810</v>
@@ -1754,13 +1749,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490844</v>
+        <v>490860</v>
       </c>
       <c r="R12" t="n">
-        <v>6864975</v>
+        <v>6864997</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1804,22 +1799,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124324335</v>
+        <v>124323622</v>
       </c>
       <c r="B13" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1832,37 +1827,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490869</v>
+        <v>490832</v>
       </c>
       <c r="R13" t="n">
-        <v>6864990</v>
+        <v>6865017</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1906,19 +1901,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124324167</v>
+        <v>124323908</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -1958,13 +1953,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490860</v>
+        <v>490844</v>
       </c>
       <c r="R14" t="n">
-        <v>6864997</v>
+        <v>6864975</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2008,22 +2003,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124324981</v>
+        <v>124323613</v>
       </c>
       <c r="B15" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2036,34 +2031,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490817</v>
+        <v>490844</v>
       </c>
       <c r="R15" t="n">
-        <v>6865147</v>
+        <v>6865014</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2122,10 +2117,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124323587</v>
+        <v>124323971</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2138,34 +2133,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490850</v>
+        <v>490853</v>
       </c>
       <c r="R16" t="n">
-        <v>6865018</v>
+        <v>6865017</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2224,7 +2219,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124324899</v>
+        <v>124323575</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2260,17 +2255,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490800</v>
+        <v>490851</v>
       </c>
       <c r="R17" t="n">
-        <v>6865161</v>
+        <v>6865050</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2314,22 +2309,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124324301</v>
+        <v>124325068</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2338,25 +2333,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2366,13 +2361,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490835</v>
+        <v>490832</v>
       </c>
       <c r="R18" t="n">
-        <v>6864998</v>
+        <v>6865135</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2402,6 +2397,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2416,19 +2416,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124323613</v>
+        <v>124325022</v>
       </c>
       <c r="B19" t="n">
         <v>78810</v>
@@ -2464,17 +2464,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490844</v>
+        <v>490825</v>
       </c>
       <c r="R19" t="n">
-        <v>6865014</v>
+        <v>6865147</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2530,10 +2530,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124323716</v>
+        <v>124323858</v>
       </c>
       <c r="B20" t="n">
-        <v>79891</v>
+        <v>91579</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2542,41 +2542,50 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490841</v>
+        <v>490832</v>
       </c>
       <c r="R20" t="n">
-        <v>6865011</v>
+        <v>6865023</v>
       </c>
       <c r="S20" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2734,7 +2743,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124324110</v>
+        <v>124323587</v>
       </c>
       <c r="B22" t="n">
         <v>78810</v>
@@ -2770,14 +2779,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490853</v>
+        <v>490850</v>
       </c>
       <c r="R22" t="n">
-        <v>6865011</v>
+        <v>6865018</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2836,10 +2845,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124323858</v>
+        <v>124324272</v>
       </c>
       <c r="B23" t="n">
-        <v>91579</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2848,50 +2857,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490832</v>
+        <v>490869</v>
       </c>
       <c r="R23" t="n">
-        <v>6865023</v>
+        <v>6864990</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2935,22 +2935,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124324530</v>
+        <v>124323707</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2963,21 +2963,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2987,13 +2987,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490855</v>
+        <v>490838</v>
       </c>
       <c r="R24" t="n">
-        <v>6864955</v>
+        <v>6865007</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3037,19 +3037,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124364810</v>
+        <v>124364652</v>
       </c>
       <c r="B25" t="n">
         <v>78810</v>
@@ -3085,17 +3085,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491146</v>
+        <v>491120</v>
       </c>
       <c r="R25" t="n">
-        <v>6865207</v>
+        <v>6865386</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124365978</v>
+        <v>124365478</v>
       </c>
       <c r="B26" t="n">
         <v>78810</v>
@@ -3187,14 +3187,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kullberget, Kullberget, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490934</v>
+        <v>490807</v>
       </c>
       <c r="R26" t="n">
-        <v>6865221</v>
+        <v>6865148</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3224,19 +3224,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>16:07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3251,19 +3241,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124365822</v>
+        <v>124365903</v>
       </c>
       <c r="B27" t="n">
         <v>78810</v>
@@ -3303,10 +3293,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490796</v>
+        <v>490934</v>
       </c>
       <c r="R27" t="n">
-        <v>6865155</v>
+        <v>6865221</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3336,9 +3326,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3353,12 +3353,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3467,7 +3467,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124365206</v>
+        <v>124364810</v>
       </c>
       <c r="B29" t="n">
         <v>78810</v>
@@ -3507,10 +3507,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491179</v>
+        <v>491146</v>
       </c>
       <c r="R29" t="n">
-        <v>6865114</v>
+        <v>6865207</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3569,10 +3569,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124365787</v>
+        <v>124364496</v>
       </c>
       <c r="B30" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3585,37 +3585,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490822</v>
+        <v>491193</v>
       </c>
       <c r="R30" t="n">
-        <v>6865151</v>
+        <v>6865330</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3671,10 +3671,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124365478</v>
+        <v>124365787</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3687,21 +3687,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3711,13 +3711,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490807</v>
+        <v>490822</v>
       </c>
       <c r="R31" t="n">
-        <v>6865148</v>
+        <v>6865151</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124364652</v>
+        <v>124365822</v>
       </c>
       <c r="B32" t="n">
         <v>78810</v>
@@ -3809,17 +3809,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>491120</v>
+        <v>490796</v>
       </c>
       <c r="R32" t="n">
-        <v>6865386</v>
+        <v>6865155</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124364496</v>
+        <v>124365206</v>
       </c>
       <c r="B33" t="n">
         <v>78810</v>
@@ -3911,14 +3911,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>491193</v>
+        <v>491179</v>
       </c>
       <c r="R33" t="n">
-        <v>6865330</v>
+        <v>6865114</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>

--- a/artfynd/A 24249-2024 artfynd.xlsx
+++ b/artfynd/A 24249-2024 artfynd.xlsx
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124324301</v>
+        <v>124324899</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490835</v>
+        <v>490800</v>
       </c>
       <c r="R3" t="n">
-        <v>6864998</v>
+        <v>6865161</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,22 +876,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124324981</v>
+        <v>124323716</v>
       </c>
       <c r="B4" t="n">
-        <v>79892</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,21 +904,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,13 +928,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490817</v>
+        <v>490841</v>
       </c>
       <c r="R4" t="n">
-        <v>6865147</v>
+        <v>6865011</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,19 +978,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124324530</v>
+        <v>124324192</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490855</v>
+        <v>490878</v>
       </c>
       <c r="R5" t="n">
-        <v>6864955</v>
+        <v>6864994</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1092,7 +1092,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124324110</v>
+        <v>124323587</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1128,14 +1128,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490853</v>
+        <v>490850</v>
       </c>
       <c r="R6" t="n">
-        <v>6865011</v>
+        <v>6865018</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1194,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124323891</v>
+        <v>124324393</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>78889</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1210,21 +1210,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1234,13 +1234,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490832</v>
+        <v>490851</v>
       </c>
       <c r="R7" t="n">
-        <v>6865023</v>
+        <v>6864963</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1270,11 +1270,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-22</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1301,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124324335</v>
+        <v>124324167</v>
       </c>
       <c r="B8" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1317,21 +1312,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1341,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490869</v>
+        <v>490860</v>
       </c>
       <c r="R8" t="n">
-        <v>6864990</v>
+        <v>6864997</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1403,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124323716</v>
+        <v>124324335</v>
       </c>
       <c r="B9" t="n">
-        <v>79891</v>
+        <v>74901</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1419,21 +1414,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1443,13 +1438,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490841</v>
+        <v>490869</v>
       </c>
       <c r="R9" t="n">
-        <v>6865011</v>
+        <v>6864990</v>
       </c>
       <c r="S9" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1493,22 +1488,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124324192</v>
+        <v>124323858</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>91579</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,41 +1512,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490878</v>
+        <v>490832</v>
       </c>
       <c r="R10" t="n">
-        <v>6864994</v>
+        <v>6865023</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1595,22 +1599,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124324899</v>
+        <v>124324981</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1623,21 +1627,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1647,13 +1651,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490800</v>
+        <v>490817</v>
       </c>
       <c r="R11" t="n">
-        <v>6865161</v>
+        <v>6865147</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1709,10 +1713,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124324167</v>
+        <v>124323707</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1725,21 +1729,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1749,13 +1753,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490860</v>
+        <v>490838</v>
       </c>
       <c r="R12" t="n">
-        <v>6864997</v>
+        <v>6865007</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1799,19 +1803,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124323622</v>
+        <v>124324301</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -1847,14 +1851,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490832</v>
+        <v>490835</v>
       </c>
       <c r="R13" t="n">
-        <v>6865017</v>
+        <v>6864998</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1913,10 +1917,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124323908</v>
+        <v>124323891</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1929,21 +1933,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1953,13 +1957,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490844</v>
+        <v>490832</v>
       </c>
       <c r="R14" t="n">
-        <v>6864975</v>
+        <v>6865023</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1989,6 +1993,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2003,22 +2012,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124323613</v>
+        <v>124325068</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2027,38 +2036,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490844</v>
+        <v>490832</v>
       </c>
       <c r="R15" t="n">
-        <v>6865014</v>
+        <v>6865135</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2091,6 +2100,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2117,10 +2131,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124323971</v>
+        <v>124325022</v>
       </c>
       <c r="B16" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2133,21 +2147,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2157,13 +2171,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490853</v>
+        <v>490825</v>
       </c>
       <c r="R16" t="n">
-        <v>6865017</v>
+        <v>6865147</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2219,7 +2233,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124323575</v>
+        <v>124324272</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2255,17 +2269,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490851</v>
+        <v>490869</v>
       </c>
       <c r="R17" t="n">
-        <v>6865050</v>
+        <v>6864990</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2309,22 +2323,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124325068</v>
+        <v>124324530</v>
       </c>
       <c r="B18" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2333,25 +2347,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2361,10 +2375,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490832</v>
+        <v>490855</v>
       </c>
       <c r="R18" t="n">
-        <v>6865135</v>
+        <v>6864955</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2397,11 +2411,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-22</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2428,7 +2437,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124325022</v>
+        <v>124324110</v>
       </c>
       <c r="B19" t="n">
         <v>78810</v>
@@ -2468,13 +2477,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490825</v>
+        <v>490853</v>
       </c>
       <c r="R19" t="n">
-        <v>6865147</v>
+        <v>6865011</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2530,10 +2539,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124323858</v>
+        <v>124323622</v>
       </c>
       <c r="B20" t="n">
-        <v>91579</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2542,50 +2551,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q20" t="n">
         <v>490832</v>
       </c>
       <c r="R20" t="n">
-        <v>6865023</v>
+        <v>6865017</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2641,10 +2641,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124324393</v>
+        <v>124323971</v>
       </c>
       <c r="B21" t="n">
-        <v>78889</v>
+        <v>78546</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2657,21 +2657,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>864</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2681,10 +2681,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490851</v>
+        <v>490853</v>
       </c>
       <c r="R21" t="n">
-        <v>6864963</v>
+        <v>6865017</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2743,7 +2743,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124323587</v>
+        <v>124323575</v>
       </c>
       <c r="B22" t="n">
         <v>78810</v>
@@ -2783,13 +2783,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490850</v>
+        <v>490851</v>
       </c>
       <c r="R22" t="n">
-        <v>6865018</v>
+        <v>6865050</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2833,19 +2833,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124324272</v>
+        <v>124323908</v>
       </c>
       <c r="B23" t="n">
         <v>78810</v>
@@ -2885,13 +2885,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490869</v>
+        <v>490844</v>
       </c>
       <c r="R23" t="n">
-        <v>6864990</v>
+        <v>6864975</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2935,22 +2935,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124323707</v>
+        <v>124323613</v>
       </c>
       <c r="B24" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2963,37 +2963,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490838</v>
+        <v>490844</v>
       </c>
       <c r="R24" t="n">
-        <v>6865007</v>
+        <v>6865014</v>
       </c>
       <c r="S24" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3037,19 +3037,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124364652</v>
+        <v>124365206</v>
       </c>
       <c r="B25" t="n">
         <v>78810</v>
@@ -3085,17 +3085,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491120</v>
+        <v>491179</v>
       </c>
       <c r="R25" t="n">
-        <v>6865386</v>
+        <v>6865114</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124365478</v>
+        <v>124364810</v>
       </c>
       <c r="B26" t="n">
         <v>78810</v>
@@ -3191,10 +3191,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490807</v>
+        <v>491146</v>
       </c>
       <c r="R26" t="n">
-        <v>6865148</v>
+        <v>6865207</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3253,7 +3253,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124365903</v>
+        <v>124364652</v>
       </c>
       <c r="B27" t="n">
         <v>78810</v>
@@ -3289,17 +3289,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490934</v>
+        <v>491120</v>
       </c>
       <c r="R27" t="n">
-        <v>6865221</v>
+        <v>6865386</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3326,19 +3326,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>16:02</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>16:02</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3353,12 +3343,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3467,7 +3457,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124364810</v>
+        <v>124365978</v>
       </c>
       <c r="B29" t="n">
         <v>78810</v>
@@ -3503,14 +3493,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Kullberget, Kullberget, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491146</v>
+        <v>490934</v>
       </c>
       <c r="R29" t="n">
-        <v>6865207</v>
+        <v>6865221</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3540,9 +3530,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3557,19 +3557,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124364496</v>
+        <v>124365822</v>
       </c>
       <c r="B30" t="n">
         <v>78810</v>
@@ -3605,14 +3605,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>491193</v>
+        <v>490796</v>
       </c>
       <c r="R30" t="n">
-        <v>6865330</v>
+        <v>6865155</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3773,7 +3773,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124365822</v>
+        <v>124365478</v>
       </c>
       <c r="B32" t="n">
         <v>78810</v>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490796</v>
+        <v>490807</v>
       </c>
       <c r="R32" t="n">
-        <v>6865155</v>
+        <v>6865148</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3875,7 +3875,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124365206</v>
+        <v>124364496</v>
       </c>
       <c r="B33" t="n">
         <v>78810</v>
@@ -3911,14 +3911,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>491179</v>
+        <v>491193</v>
       </c>
       <c r="R33" t="n">
-        <v>6865114</v>
+        <v>6865330</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>

--- a/artfynd/A 24249-2024 artfynd.xlsx
+++ b/artfynd/A 24249-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124324899</v>
+        <v>124323716</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,13 +826,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490800</v>
+        <v>490841</v>
       </c>
       <c r="R3" t="n">
-        <v>6865161</v>
+        <v>6865011</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,22 +876,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124323716</v>
+        <v>124324899</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,21 +904,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,13 +928,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490841</v>
+        <v>490800</v>
       </c>
       <c r="R4" t="n">
-        <v>6865011</v>
+        <v>6865161</v>
       </c>
       <c r="S4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,12 +978,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 24249-2024 artfynd.xlsx
+++ b/artfynd/A 24249-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124323716</v>
+        <v>124324167</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,13 +826,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490841</v>
+        <v>490860</v>
       </c>
       <c r="R3" t="n">
-        <v>6865011</v>
+        <v>6864997</v>
       </c>
       <c r="S3" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,19 +876,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124324899</v>
+        <v>124323908</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -928,13 +928,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490800</v>
+        <v>490844</v>
       </c>
       <c r="R4" t="n">
-        <v>6865161</v>
+        <v>6864975</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,22 +978,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124324192</v>
+        <v>124323858</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>91579</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,41 +1002,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490878</v>
+        <v>490832</v>
       </c>
       <c r="R5" t="n">
-        <v>6864994</v>
+        <v>6865023</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,22 +1089,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124323587</v>
+        <v>124324335</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1108,34 +1117,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490850</v>
+        <v>490869</v>
       </c>
       <c r="R6" t="n">
-        <v>6865018</v>
+        <v>6864990</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1194,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124324393</v>
+        <v>124323575</v>
       </c>
       <c r="B7" t="n">
-        <v>78889</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1210,37 +1219,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
         <v>490851</v>
       </c>
       <c r="R7" t="n">
-        <v>6864963</v>
+        <v>6865050</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1284,19 +1293,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124324167</v>
+        <v>124324301</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1336,13 +1345,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490860</v>
+        <v>490835</v>
       </c>
       <c r="R8" t="n">
-        <v>6864997</v>
+        <v>6864998</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1386,22 +1395,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124324335</v>
+        <v>124325068</v>
       </c>
       <c r="B9" t="n">
-        <v>74901</v>
+        <v>56722</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,25 +1419,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1438,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490869</v>
+        <v>490832</v>
       </c>
       <c r="R9" t="n">
-        <v>6864990</v>
+        <v>6865135</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1474,6 +1483,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1500,10 +1514,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124323858</v>
+        <v>124323613</v>
       </c>
       <c r="B10" t="n">
-        <v>91579</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,50 +1526,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490832</v>
+        <v>490844</v>
       </c>
       <c r="R10" t="n">
-        <v>6865023</v>
+        <v>6865014</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1599,22 +1604,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124324981</v>
+        <v>124323716</v>
       </c>
       <c r="B11" t="n">
-        <v>79892</v>
+        <v>79891</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1627,21 +1632,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1651,13 +1656,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490817</v>
+        <v>490841</v>
       </c>
       <c r="R11" t="n">
-        <v>6865147</v>
+        <v>6865011</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1701,22 +1706,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124323707</v>
+        <v>124324110</v>
       </c>
       <c r="B12" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1729,21 +1734,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1753,13 +1758,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490838</v>
+        <v>490853</v>
       </c>
       <c r="R12" t="n">
-        <v>6865007</v>
+        <v>6865011</v>
       </c>
       <c r="S12" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1803,19 +1808,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124324301</v>
+        <v>124324192</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -1855,13 +1860,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490835</v>
+        <v>490878</v>
       </c>
       <c r="R13" t="n">
-        <v>6864998</v>
+        <v>6864994</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1905,22 +1910,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124323891</v>
+        <v>124323622</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1933,34 +1938,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
         <v>490832</v>
       </c>
       <c r="R14" t="n">
-        <v>6865023</v>
+        <v>6865017</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1995,11 +2000,6 @@
           <t>2025-04-22</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2012,22 +2012,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124325068</v>
+        <v>124324530</v>
       </c>
       <c r="B15" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2036,25 +2036,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490832</v>
+        <v>490855</v>
       </c>
       <c r="R15" t="n">
-        <v>6865135</v>
+        <v>6864955</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2100,11 +2100,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-22</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2131,10 +2126,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124325022</v>
+        <v>124323891</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2147,21 +2142,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2171,10 +2166,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490825</v>
+        <v>490832</v>
       </c>
       <c r="R16" t="n">
-        <v>6865147</v>
+        <v>6865023</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2207,6 +2202,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2233,10 +2233,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124324272</v>
+        <v>124324393</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>78889</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2249,21 +2249,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2273,10 +2273,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490869</v>
+        <v>490851</v>
       </c>
       <c r="R17" t="n">
-        <v>6864990</v>
+        <v>6864963</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2335,10 +2335,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124324530</v>
+        <v>124323707</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2351,21 +2351,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2375,13 +2375,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490855</v>
+        <v>490838</v>
       </c>
       <c r="R18" t="n">
-        <v>6864955</v>
+        <v>6865007</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2425,19 +2425,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124324110</v>
+        <v>124324272</v>
       </c>
       <c r="B19" t="n">
         <v>78810</v>
@@ -2477,10 +2477,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490853</v>
+        <v>490869</v>
       </c>
       <c r="R19" t="n">
-        <v>6865011</v>
+        <v>6864990</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2539,7 +2539,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124323622</v>
+        <v>124324899</v>
       </c>
       <c r="B20" t="n">
         <v>78810</v>
@@ -2575,14 +2575,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490832</v>
+        <v>490800</v>
       </c>
       <c r="R20" t="n">
-        <v>6865017</v>
+        <v>6865161</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2629,22 +2629,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124323971</v>
+        <v>124324981</v>
       </c>
       <c r="B21" t="n">
-        <v>78546</v>
+        <v>79892</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2657,21 +2657,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2681,10 +2681,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490853</v>
+        <v>490817</v>
       </c>
       <c r="R21" t="n">
-        <v>6865017</v>
+        <v>6865147</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2743,7 +2743,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124323575</v>
+        <v>124323587</v>
       </c>
       <c r="B22" t="n">
         <v>78810</v>
@@ -2783,13 +2783,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490851</v>
+        <v>490850</v>
       </c>
       <c r="R22" t="n">
-        <v>6865050</v>
+        <v>6865018</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2833,19 +2833,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124323908</v>
+        <v>124325022</v>
       </c>
       <c r="B23" t="n">
         <v>78810</v>
@@ -2885,13 +2885,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490844</v>
+        <v>490825</v>
       </c>
       <c r="R23" t="n">
-        <v>6864975</v>
+        <v>6865147</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2935,22 +2935,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124323613</v>
+        <v>124323971</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2963,34 +2963,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490844</v>
+        <v>490853</v>
       </c>
       <c r="R24" t="n">
-        <v>6865014</v>
+        <v>6865017</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3151,7 +3151,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124364810</v>
+        <v>124364652</v>
       </c>
       <c r="B26" t="n">
         <v>78810</v>
@@ -3187,17 +3187,17 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>491146</v>
+        <v>491120</v>
       </c>
       <c r="R26" t="n">
-        <v>6865207</v>
+        <v>6865386</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124364652</v>
+        <v>124365978</v>
       </c>
       <c r="B27" t="n">
         <v>78810</v>
@@ -3289,17 +3289,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullberget, Kullberget, Hls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491120</v>
+        <v>490934</v>
       </c>
       <c r="R27" t="n">
-        <v>6865386</v>
+        <v>6865221</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3326,9 +3326,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3343,22 +3353,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124364538</v>
+        <v>124365787</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3371,37 +3381,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>491166</v>
+        <v>490822</v>
       </c>
       <c r="R28" t="n">
-        <v>6865362</v>
+        <v>6865151</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3457,7 +3467,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124365978</v>
+        <v>124365478</v>
       </c>
       <c r="B29" t="n">
         <v>78810</v>
@@ -3493,14 +3503,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kullberget, Kullberget, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490934</v>
+        <v>490807</v>
       </c>
       <c r="R29" t="n">
-        <v>6865221</v>
+        <v>6865148</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3530,19 +3540,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>16:07</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3557,12 +3557,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3671,10 +3671,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124365787</v>
+        <v>124364538</v>
       </c>
       <c r="B31" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3687,37 +3687,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490822</v>
+        <v>491166</v>
       </c>
       <c r="R31" t="n">
-        <v>6865151</v>
+        <v>6865362</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124365478</v>
+        <v>124364810</v>
       </c>
       <c r="B32" t="n">
         <v>78810</v>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490807</v>
+        <v>491146</v>
       </c>
       <c r="R32" t="n">
-        <v>6865148</v>
+        <v>6865207</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4081,6 +4081,354 @@
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>124364917</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79428</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Kullvallen, Kullvallen, Hls</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>491032</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6865166</v>
+      </c>
+      <c r="S35" t="n">
+        <v>15</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Ängersjö</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>124364256</v>
+      </c>
+      <c r="B36" t="n">
+        <v>56722</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Kullvallen, Kullvallen, Hls</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>490962</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6865124</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ängersjö</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>124364664</v>
+      </c>
+      <c r="B37" t="n">
+        <v>77738</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Kullvallen, Kullvallen, Hls</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>491024</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6865165</v>
+      </c>
+      <c r="S37" t="n">
+        <v>15</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Ängersjö</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24249-2024 artfynd.xlsx
+++ b/artfynd/A 24249-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124324167</v>
+        <v>124324393</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>78889</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490860</v>
+        <v>490851</v>
       </c>
       <c r="R3" t="n">
-        <v>6864997</v>
+        <v>6864963</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -888,7 +888,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124323908</v>
+        <v>124324301</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -928,13 +928,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490844</v>
+        <v>490835</v>
       </c>
       <c r="R4" t="n">
-        <v>6864975</v>
+        <v>6864998</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124323858</v>
+        <v>124323971</v>
       </c>
       <c r="B5" t="n">
-        <v>91579</v>
+        <v>78546</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,50 +1002,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>760</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490832</v>
+        <v>490853</v>
       </c>
       <c r="R5" t="n">
-        <v>6865023</v>
+        <v>6865017</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1089,22 +1080,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124324335</v>
+        <v>124323908</v>
       </c>
       <c r="B6" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1117,21 +1108,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,13 +1132,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490869</v>
+        <v>490844</v>
       </c>
       <c r="R6" t="n">
-        <v>6864990</v>
+        <v>6864975</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1191,22 +1182,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124323575</v>
+        <v>124324981</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1219,37 +1210,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490851</v>
+        <v>490817</v>
       </c>
       <c r="R7" t="n">
-        <v>6865050</v>
+        <v>6865147</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1293,19 +1284,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124324301</v>
+        <v>124325022</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1345,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490835</v>
+        <v>490825</v>
       </c>
       <c r="R8" t="n">
-        <v>6864998</v>
+        <v>6865147</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1395,22 +1386,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124325068</v>
+        <v>124324192</v>
       </c>
       <c r="B9" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1419,25 +1410,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1447,10 +1438,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490832</v>
+        <v>490878</v>
       </c>
       <c r="R9" t="n">
-        <v>6865135</v>
+        <v>6864994</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1483,11 +1474,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-22</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1514,7 +1500,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124323613</v>
+        <v>124324899</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1550,17 +1536,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490844</v>
+        <v>490800</v>
       </c>
       <c r="R10" t="n">
-        <v>6865014</v>
+        <v>6865161</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1616,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124323716</v>
+        <v>124323622</v>
       </c>
       <c r="B11" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1632,37 +1618,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490841</v>
+        <v>490832</v>
       </c>
       <c r="R11" t="n">
-        <v>6865011</v>
+        <v>6865017</v>
       </c>
       <c r="S11" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1718,10 +1704,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124324110</v>
+        <v>124323891</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1734,21 +1720,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1758,13 +1744,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490853</v>
+        <v>490832</v>
       </c>
       <c r="R12" t="n">
-        <v>6865011</v>
+        <v>6865023</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1794,6 +1780,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1820,10 +1811,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124324192</v>
+        <v>124323716</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1836,21 +1827,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1860,13 +1851,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490878</v>
+        <v>490841</v>
       </c>
       <c r="R13" t="n">
-        <v>6864994</v>
+        <v>6865011</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1910,22 +1901,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124323622</v>
+        <v>124325068</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1934,41 +1925,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
         <v>490832</v>
       </c>
       <c r="R14" t="n">
-        <v>6865017</v>
+        <v>6865135</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1998,6 +1989,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2012,19 +2008,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124324530</v>
+        <v>124324167</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2064,10 +2060,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490855</v>
+        <v>490860</v>
       </c>
       <c r="R15" t="n">
-        <v>6864955</v>
+        <v>6864997</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2126,10 +2122,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124323891</v>
+        <v>124323707</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>79892</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2142,21 +2138,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2166,13 +2162,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490832</v>
+        <v>490838</v>
       </c>
       <c r="R16" t="n">
-        <v>6865023</v>
+        <v>6865007</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2202,11 +2198,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-22</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2221,22 +2212,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124324393</v>
+        <v>124324530</v>
       </c>
       <c r="B17" t="n">
-        <v>78889</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2249,21 +2240,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2273,10 +2264,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490851</v>
+        <v>490855</v>
       </c>
       <c r="R17" t="n">
-        <v>6864963</v>
+        <v>6864955</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2335,10 +2326,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124323707</v>
+        <v>124324335</v>
       </c>
       <c r="B18" t="n">
-        <v>79892</v>
+        <v>74901</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2351,21 +2342,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2375,13 +2366,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490838</v>
+        <v>490869</v>
       </c>
       <c r="R18" t="n">
-        <v>6865007</v>
+        <v>6864990</v>
       </c>
       <c r="S18" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2425,19 +2416,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124324272</v>
+        <v>124323587</v>
       </c>
       <c r="B19" t="n">
         <v>78810</v>
@@ -2473,14 +2464,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490869</v>
+        <v>490850</v>
       </c>
       <c r="R19" t="n">
-        <v>6864990</v>
+        <v>6865018</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2539,10 +2530,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124324899</v>
+        <v>124323858</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>91579</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2551,41 +2542,50 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490800</v>
+        <v>490832</v>
       </c>
       <c r="R20" t="n">
-        <v>6865161</v>
+        <v>6865023</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2629,22 +2629,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124324981</v>
+        <v>124323613</v>
       </c>
       <c r="B21" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2657,34 +2657,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490817</v>
+        <v>490844</v>
       </c>
       <c r="R21" t="n">
-        <v>6865147</v>
+        <v>6865014</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2743,7 +2743,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124323587</v>
+        <v>124324272</v>
       </c>
       <c r="B22" t="n">
         <v>78810</v>
@@ -2779,14 +2779,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490850</v>
+        <v>490869</v>
       </c>
       <c r="R22" t="n">
-        <v>6865018</v>
+        <v>6864990</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2845,7 +2845,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124325022</v>
+        <v>124323575</v>
       </c>
       <c r="B23" t="n">
         <v>78810</v>
@@ -2881,17 +2881,17 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490825</v>
+        <v>490851</v>
       </c>
       <c r="R23" t="n">
-        <v>6865147</v>
+        <v>6865050</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2935,22 +2935,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124323971</v>
+        <v>124324110</v>
       </c>
       <c r="B24" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2963,21 +2963,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2990,7 +2990,7 @@
         <v>490853</v>
       </c>
       <c r="R24" t="n">
-        <v>6865017</v>
+        <v>6865011</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3049,7 +3049,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124365206</v>
+        <v>124365478</v>
       </c>
       <c r="B25" t="n">
         <v>78810</v>
@@ -3089,10 +3089,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491179</v>
+        <v>490807</v>
       </c>
       <c r="R25" t="n">
-        <v>6865114</v>
+        <v>6865148</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3151,10 +3151,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124364652</v>
+        <v>124365787</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3167,34 +3167,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>491120</v>
+        <v>490822</v>
       </c>
       <c r="R26" t="n">
-        <v>6865386</v>
+        <v>6865151</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3365,10 +3365,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124365787</v>
+        <v>124365822</v>
       </c>
       <c r="B28" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3381,21 +3381,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3405,13 +3405,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490822</v>
+        <v>490796</v>
       </c>
       <c r="R28" t="n">
-        <v>6865151</v>
+        <v>6865155</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124365478</v>
+        <v>124364652</v>
       </c>
       <c r="B29" t="n">
         <v>78810</v>
@@ -3503,17 +3503,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490807</v>
+        <v>491120</v>
       </c>
       <c r="R29" t="n">
-        <v>6865148</v>
+        <v>6865386</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124365822</v>
+        <v>124364538</v>
       </c>
       <c r="B30" t="n">
         <v>78810</v>
@@ -3605,14 +3605,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490796</v>
+        <v>491166</v>
       </c>
       <c r="R30" t="n">
-        <v>6865155</v>
+        <v>6865362</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3671,7 +3671,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124364538</v>
+        <v>124365206</v>
       </c>
       <c r="B31" t="n">
         <v>78810</v>
@@ -3707,14 +3707,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>491166</v>
+        <v>491179</v>
       </c>
       <c r="R31" t="n">
-        <v>6865362</v>
+        <v>6865114</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3773,7 +3773,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124364810</v>
+        <v>124364496</v>
       </c>
       <c r="B32" t="n">
         <v>78810</v>
@@ -3809,14 +3809,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>491146</v>
+        <v>491193</v>
       </c>
       <c r="R32" t="n">
-        <v>6865207</v>
+        <v>6865330</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3875,7 +3875,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124364496</v>
+        <v>124364810</v>
       </c>
       <c r="B33" t="n">
         <v>78810</v>
@@ -3911,14 +3911,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>491193</v>
+        <v>491146</v>
       </c>
       <c r="R33" t="n">
-        <v>6865330</v>
+        <v>6865207</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4083,10 +4083,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124364917</v>
+        <v>124364256</v>
       </c>
       <c r="B35" t="n">
-        <v>79428</v>
+        <v>56722</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4095,41 +4095,53 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>491032</v>
+        <v>490962</v>
       </c>
       <c r="R35" t="n">
-        <v>6865166</v>
+        <v>6865124</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4158,7 +4170,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4168,7 +4180,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4195,10 +4207,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124364256</v>
+        <v>124364664</v>
       </c>
       <c r="B36" t="n">
-        <v>56722</v>
+        <v>77738</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4207,53 +4219,41 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100138</v>
+        <v>6487</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490962</v>
+        <v>491024</v>
       </c>
       <c r="R36" t="n">
-        <v>6865124</v>
+        <v>6865165</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4319,10 +4319,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124364664</v>
+        <v>124364917</v>
       </c>
       <c r="B37" t="n">
-        <v>77738</v>
+        <v>79428</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4335,21 +4335,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4359,10 +4359,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>491024</v>
+        <v>491032</v>
       </c>
       <c r="R37" t="n">
-        <v>6865165</v>
+        <v>6865166</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4394,7 +4394,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 24249-2024 artfynd.xlsx
+++ b/artfynd/A 24249-2024 artfynd.xlsx
@@ -3467,7 +3467,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124364652</v>
+        <v>124364538</v>
       </c>
       <c r="B29" t="n">
         <v>78810</v>
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491120</v>
+        <v>491166</v>
       </c>
       <c r="R29" t="n">
-        <v>6865386</v>
+        <v>6865362</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124364538</v>
+        <v>124364652</v>
       </c>
       <c r="B30" t="n">
         <v>78810</v>
@@ -3609,13 +3609,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>491166</v>
+        <v>491120</v>
       </c>
       <c r="R30" t="n">
-        <v>6865362</v>
+        <v>6865386</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>

--- a/artfynd/A 24249-2024 artfynd.xlsx
+++ b/artfynd/A 24249-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124324393</v>
+        <v>124324301</v>
       </c>
       <c r="B3" t="n">
-        <v>78889</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,13 +826,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490851</v>
+        <v>490835</v>
       </c>
       <c r="R3" t="n">
-        <v>6864963</v>
+        <v>6864998</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,22 +876,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124324301</v>
+        <v>124324335</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,21 +904,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,13 +928,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490835</v>
+        <v>490869</v>
       </c>
       <c r="R4" t="n">
-        <v>6864998</v>
+        <v>6864990</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,22 +978,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124323971</v>
+        <v>124324272</v>
       </c>
       <c r="B5" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,21 +1006,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490853</v>
+        <v>490869</v>
       </c>
       <c r="R5" t="n">
-        <v>6865017</v>
+        <v>6864990</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1092,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124323908</v>
+        <v>124325068</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,25 +1104,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,13 +1132,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490844</v>
+        <v>490832</v>
       </c>
       <c r="R6" t="n">
-        <v>6864975</v>
+        <v>6865135</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1168,6 +1168,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1182,22 +1187,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124324981</v>
+        <v>124323891</v>
       </c>
       <c r="B7" t="n">
-        <v>79892</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1210,21 +1215,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1234,13 +1239,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490817</v>
+        <v>490832</v>
       </c>
       <c r="R7" t="n">
-        <v>6865147</v>
+        <v>6865023</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1270,6 +1275,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1296,10 +1306,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124325022</v>
+        <v>124323716</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1312,21 +1322,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,13 +1346,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490825</v>
+        <v>490841</v>
       </c>
       <c r="R8" t="n">
-        <v>6865147</v>
+        <v>6865011</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1386,19 +1396,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124324192</v>
+        <v>124324899</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1438,13 +1448,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490878</v>
+        <v>490800</v>
       </c>
       <c r="R9" t="n">
-        <v>6864994</v>
+        <v>6865161</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1500,10 +1510,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124324899</v>
+        <v>124323707</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1516,21 +1526,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,13 +1550,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490800</v>
+        <v>490838</v>
       </c>
       <c r="R10" t="n">
-        <v>6865161</v>
+        <v>6865007</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1590,22 +1600,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124323622</v>
+        <v>124324981</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1618,37 +1628,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490832</v>
+        <v>490817</v>
       </c>
       <c r="R11" t="n">
-        <v>6865017</v>
+        <v>6865147</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1692,22 +1702,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124323891</v>
+        <v>124324110</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1720,21 +1730,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1744,13 +1754,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490832</v>
+        <v>490853</v>
       </c>
       <c r="R12" t="n">
-        <v>6865023</v>
+        <v>6865011</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1780,11 +1790,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-22</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1811,10 +1816,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124323716</v>
+        <v>124324167</v>
       </c>
       <c r="B13" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1827,21 +1832,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1851,13 +1856,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490841</v>
+        <v>490860</v>
       </c>
       <c r="R13" t="n">
-        <v>6865011</v>
+        <v>6864997</v>
       </c>
       <c r="S13" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1901,22 +1906,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124325068</v>
+        <v>124323613</v>
       </c>
       <c r="B14" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1925,38 +1930,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490832</v>
+        <v>490844</v>
       </c>
       <c r="R14" t="n">
-        <v>6865135</v>
+        <v>6865014</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1989,11 +1994,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-22</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2020,7 +2020,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124324167</v>
+        <v>124323908</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2060,13 +2060,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490860</v>
+        <v>490844</v>
       </c>
       <c r="R15" t="n">
-        <v>6864997</v>
+        <v>6864975</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2110,22 +2110,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124323707</v>
+        <v>124323587</v>
       </c>
       <c r="B16" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2138,37 +2138,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490838</v>
+        <v>490850</v>
       </c>
       <c r="R16" t="n">
-        <v>6865007</v>
+        <v>6865018</v>
       </c>
       <c r="S16" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2212,19 +2212,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124324530</v>
+        <v>124324192</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2264,10 +2264,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490855</v>
+        <v>490878</v>
       </c>
       <c r="R17" t="n">
-        <v>6864955</v>
+        <v>6864994</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2326,10 +2326,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124324335</v>
+        <v>124323971</v>
       </c>
       <c r="B18" t="n">
-        <v>74901</v>
+        <v>78546</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2342,21 +2342,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2366,10 +2366,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490869</v>
+        <v>490853</v>
       </c>
       <c r="R18" t="n">
-        <v>6864990</v>
+        <v>6865017</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2428,7 +2428,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124323587</v>
+        <v>124325022</v>
       </c>
       <c r="B19" t="n">
         <v>78810</v>
@@ -2464,17 +2464,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490850</v>
+        <v>490825</v>
       </c>
       <c r="R19" t="n">
-        <v>6865018</v>
+        <v>6865147</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124323613</v>
+        <v>124324530</v>
       </c>
       <c r="B21" t="n">
         <v>78810</v>
@@ -2677,14 +2677,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490844</v>
+        <v>490855</v>
       </c>
       <c r="R21" t="n">
-        <v>6865014</v>
+        <v>6864955</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2743,7 +2743,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124324272</v>
+        <v>124323575</v>
       </c>
       <c r="B22" t="n">
         <v>78810</v>
@@ -2779,17 +2779,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490869</v>
+        <v>490851</v>
       </c>
       <c r="R22" t="n">
-        <v>6864990</v>
+        <v>6865050</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2833,22 +2833,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124323575</v>
+        <v>124324393</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>78889</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2861,37 +2861,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q23" t="n">
         <v>490851</v>
       </c>
       <c r="R23" t="n">
-        <v>6865050</v>
+        <v>6864963</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2935,19 +2935,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124324110</v>
+        <v>124323622</v>
       </c>
       <c r="B24" t="n">
         <v>78810</v>
@@ -2983,17 +2983,17 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490853</v>
+        <v>490832</v>
       </c>
       <c r="R24" t="n">
-        <v>6865011</v>
+        <v>6865017</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3037,19 +3037,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124365478</v>
+        <v>124364496</v>
       </c>
       <c r="B25" t="n">
         <v>78810</v>
@@ -3085,14 +3085,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490807</v>
+        <v>491193</v>
       </c>
       <c r="R25" t="n">
-        <v>6865148</v>
+        <v>6865330</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3151,10 +3151,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124365787</v>
+        <v>124364810</v>
       </c>
       <c r="B26" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3167,21 +3167,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3191,13 +3191,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490822</v>
+        <v>491146</v>
       </c>
       <c r="R26" t="n">
-        <v>6865151</v>
+        <v>6865207</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124365978</v>
+        <v>124364538</v>
       </c>
       <c r="B27" t="n">
         <v>78810</v>
@@ -3289,14 +3289,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kullberget, Kullberget, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490934</v>
+        <v>491166</v>
       </c>
       <c r="R27" t="n">
-        <v>6865221</v>
+        <v>6865362</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3326,19 +3326,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>16:07</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3353,19 +3343,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124365822</v>
+        <v>124365903</v>
       </c>
       <c r="B28" t="n">
         <v>78810</v>
@@ -3405,10 +3395,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490796</v>
+        <v>490934</v>
       </c>
       <c r="R28" t="n">
-        <v>6865155</v>
+        <v>6865221</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3438,9 +3428,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3455,19 +3455,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124364538</v>
+        <v>124365206</v>
       </c>
       <c r="B29" t="n">
         <v>78810</v>
@@ -3503,14 +3503,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491166</v>
+        <v>491179</v>
       </c>
       <c r="R29" t="n">
-        <v>6865362</v>
+        <v>6865114</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3569,7 +3569,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124364652</v>
+        <v>124365822</v>
       </c>
       <c r="B30" t="n">
         <v>78810</v>
@@ -3605,17 +3605,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>491120</v>
+        <v>490796</v>
       </c>
       <c r="R30" t="n">
-        <v>6865386</v>
+        <v>6865155</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124365206</v>
+        <v>124365478</v>
       </c>
       <c r="B31" t="n">
         <v>78810</v>
@@ -3711,10 +3711,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>491179</v>
+        <v>490807</v>
       </c>
       <c r="R31" t="n">
-        <v>6865114</v>
+        <v>6865148</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3773,7 +3773,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124364496</v>
+        <v>124364652</v>
       </c>
       <c r="B32" t="n">
         <v>78810</v>
@@ -3813,13 +3813,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>491193</v>
+        <v>491120</v>
       </c>
       <c r="R32" t="n">
-        <v>6865330</v>
+        <v>6865386</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3875,10 +3875,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124364810</v>
+        <v>124365787</v>
       </c>
       <c r="B33" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3891,21 +3891,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3915,13 +3915,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>491146</v>
+        <v>490822</v>
       </c>
       <c r="R33" t="n">
-        <v>6865207</v>
+        <v>6865151</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4083,10 +4083,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124364256</v>
+        <v>124364917</v>
       </c>
       <c r="B35" t="n">
-        <v>56722</v>
+        <v>79428</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4095,53 +4095,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490962</v>
+        <v>491032</v>
       </c>
       <c r="R35" t="n">
-        <v>6865124</v>
+        <v>6865166</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4170,7 +4158,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4180,7 +4168,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4319,10 +4307,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124364917</v>
+        <v>124364256</v>
       </c>
       <c r="B37" t="n">
-        <v>79428</v>
+        <v>56722</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4331,41 +4319,53 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>491032</v>
+        <v>490962</v>
       </c>
       <c r="R37" t="n">
-        <v>6865166</v>
+        <v>6865124</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 24249-2024 artfynd.xlsx
+++ b/artfynd/A 24249-2024 artfynd.xlsx
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124324301</v>
+        <v>124324530</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -826,13 +826,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490835</v>
+        <v>490855</v>
       </c>
       <c r="R3" t="n">
-        <v>6864998</v>
+        <v>6864955</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,22 +876,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124324335</v>
+        <v>124323716</v>
       </c>
       <c r="B4" t="n">
-        <v>74901</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,21 +904,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,13 +928,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490869</v>
+        <v>490841</v>
       </c>
       <c r="R4" t="n">
-        <v>6864990</v>
+        <v>6865011</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,19 +978,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124324272</v>
+        <v>124324301</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1030,13 +1030,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490869</v>
+        <v>490835</v>
       </c>
       <c r="R5" t="n">
-        <v>6864990</v>
+        <v>6864998</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,22 +1080,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124325068</v>
+        <v>124323613</v>
       </c>
       <c r="B6" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,38 +1104,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490832</v>
+        <v>490844</v>
       </c>
       <c r="R6" t="n">
-        <v>6865135</v>
+        <v>6865014</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1168,11 +1168,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-22</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1199,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124323891</v>
+        <v>124323858</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>91579</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,28 +1206,37 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kullvallen, Kullvallen, Hls</t>
@@ -1245,7 +1249,7 @@
         <v>6865023</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1275,11 +1279,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-22</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1294,22 +1293,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124323716</v>
+        <v>124323971</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
+        <v>78546</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1322,21 +1321,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1346,13 +1345,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490841</v>
+        <v>490853</v>
       </c>
       <c r="R8" t="n">
-        <v>6865011</v>
+        <v>6865017</v>
       </c>
       <c r="S8" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1396,22 +1395,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124324899</v>
+        <v>124323707</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1424,21 +1423,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1448,13 +1447,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490800</v>
+        <v>490838</v>
       </c>
       <c r="R9" t="n">
-        <v>6865161</v>
+        <v>6865007</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1498,22 +1497,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124323707</v>
+        <v>124324167</v>
       </c>
       <c r="B10" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1526,21 +1525,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1550,13 +1549,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490838</v>
+        <v>490860</v>
       </c>
       <c r="R10" t="n">
-        <v>6865007</v>
+        <v>6864997</v>
       </c>
       <c r="S10" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1600,22 +1599,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124324981</v>
+        <v>124323587</v>
       </c>
       <c r="B11" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1628,34 +1627,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490817</v>
+        <v>490850</v>
       </c>
       <c r="R11" t="n">
-        <v>6865147</v>
+        <v>6865018</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1714,10 +1713,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124324110</v>
+        <v>124324981</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1730,21 +1729,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1754,10 +1753,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490853</v>
+        <v>490817</v>
       </c>
       <c r="R12" t="n">
-        <v>6865011</v>
+        <v>6865147</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1816,7 +1815,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124324167</v>
+        <v>124325022</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -1856,13 +1855,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490860</v>
+        <v>490825</v>
       </c>
       <c r="R13" t="n">
-        <v>6864997</v>
+        <v>6865147</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1918,7 +1917,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124323613</v>
+        <v>124324192</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -1954,14 +1953,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490844</v>
+        <v>490878</v>
       </c>
       <c r="R14" t="n">
-        <v>6865014</v>
+        <v>6864994</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2020,7 +2019,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124323908</v>
+        <v>124324899</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2060,13 +2059,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490844</v>
+        <v>490800</v>
       </c>
       <c r="R15" t="n">
-        <v>6864975</v>
+        <v>6865161</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2110,22 +2109,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124323587</v>
+        <v>124324393</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>78889</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2138,34 +2137,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490850</v>
+        <v>490851</v>
       </c>
       <c r="R16" t="n">
-        <v>6865018</v>
+        <v>6864963</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2224,7 +2223,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124324192</v>
+        <v>124323622</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2260,17 +2259,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490878</v>
+        <v>490832</v>
       </c>
       <c r="R17" t="n">
-        <v>6864994</v>
+        <v>6865017</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2314,22 +2313,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124323971</v>
+        <v>124323575</v>
       </c>
       <c r="B18" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2342,37 +2341,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490853</v>
+        <v>490851</v>
       </c>
       <c r="R18" t="n">
-        <v>6865017</v>
+        <v>6865050</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2416,22 +2415,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124325022</v>
+        <v>124324335</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2444,21 +2443,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2468,13 +2467,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490825</v>
+        <v>490869</v>
       </c>
       <c r="R19" t="n">
-        <v>6865147</v>
+        <v>6864990</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2530,10 +2529,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124323858</v>
+        <v>124324272</v>
       </c>
       <c r="B20" t="n">
-        <v>91579</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2542,50 +2541,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490832</v>
+        <v>490869</v>
       </c>
       <c r="R20" t="n">
-        <v>6865023</v>
+        <v>6864990</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2629,19 +2619,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124324530</v>
+        <v>124323908</v>
       </c>
       <c r="B21" t="n">
         <v>78810</v>
@@ -2681,13 +2671,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490855</v>
+        <v>490844</v>
       </c>
       <c r="R21" t="n">
-        <v>6864955</v>
+        <v>6864975</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2731,22 +2721,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124323575</v>
+        <v>124325068</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2755,41 +2745,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490851</v>
+        <v>490832</v>
       </c>
       <c r="R22" t="n">
-        <v>6865050</v>
+        <v>6865135</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2819,6 +2809,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2833,22 +2828,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124324393</v>
+        <v>124324110</v>
       </c>
       <c r="B23" t="n">
-        <v>78889</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2861,21 +2856,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2885,10 +2880,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490851</v>
+        <v>490853</v>
       </c>
       <c r="R23" t="n">
-        <v>6864963</v>
+        <v>6865011</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2947,10 +2942,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124323622</v>
+        <v>124323891</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2963,34 +2958,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q24" t="n">
         <v>490832</v>
       </c>
       <c r="R24" t="n">
-        <v>6865017</v>
+        <v>6865023</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3025,6 +3020,11 @@
           <t>2025-04-22</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3037,19 +3037,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124364496</v>
+        <v>124364810</v>
       </c>
       <c r="B25" t="n">
         <v>78810</v>
@@ -3085,14 +3085,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491193</v>
+        <v>491146</v>
       </c>
       <c r="R25" t="n">
-        <v>6865330</v>
+        <v>6865207</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3151,7 +3151,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124364810</v>
+        <v>124365978</v>
       </c>
       <c r="B26" t="n">
         <v>78810</v>
@@ -3187,14 +3187,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Kullberget, Kullberget, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>491146</v>
+        <v>490934</v>
       </c>
       <c r="R26" t="n">
-        <v>6865207</v>
+        <v>6865221</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3224,9 +3224,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3241,19 +3251,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124364538</v>
+        <v>124365822</v>
       </c>
       <c r="B27" t="n">
         <v>78810</v>
@@ -3289,14 +3299,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491166</v>
+        <v>490796</v>
       </c>
       <c r="R27" t="n">
-        <v>6865362</v>
+        <v>6865155</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3355,7 +3365,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124365903</v>
+        <v>124365206</v>
       </c>
       <c r="B28" t="n">
         <v>78810</v>
@@ -3395,10 +3405,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490934</v>
+        <v>491179</v>
       </c>
       <c r="R28" t="n">
-        <v>6865221</v>
+        <v>6865114</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3428,19 +3438,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>16:02</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>16:02</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3455,19 +3455,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124365206</v>
+        <v>124364538</v>
       </c>
       <c r="B29" t="n">
         <v>78810</v>
@@ -3503,14 +3503,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491179</v>
+        <v>491166</v>
       </c>
       <c r="R29" t="n">
-        <v>6865114</v>
+        <v>6865362</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3569,7 +3569,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124365822</v>
+        <v>124365478</v>
       </c>
       <c r="B30" t="n">
         <v>78810</v>
@@ -3609,10 +3609,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490796</v>
+        <v>490807</v>
       </c>
       <c r="R30" t="n">
-        <v>6865155</v>
+        <v>6865148</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3671,7 +3671,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124365478</v>
+        <v>124364652</v>
       </c>
       <c r="B31" t="n">
         <v>78810</v>
@@ -3707,17 +3707,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490807</v>
+        <v>491120</v>
       </c>
       <c r="R31" t="n">
-        <v>6865148</v>
+        <v>6865386</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124364652</v>
+        <v>124364496</v>
       </c>
       <c r="B32" t="n">
         <v>78810</v>
@@ -3813,13 +3813,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>491120</v>
+        <v>491193</v>
       </c>
       <c r="R32" t="n">
-        <v>6865386</v>
+        <v>6865330</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4195,10 +4195,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124364664</v>
+        <v>124364256</v>
       </c>
       <c r="B36" t="n">
-        <v>77738</v>
+        <v>56722</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4207,41 +4207,53 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6487</v>
+        <v>100138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>491024</v>
+        <v>490962</v>
       </c>
       <c r="R36" t="n">
-        <v>6865165</v>
+        <v>6865124</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4270,7 +4282,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4280,7 +4292,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4307,10 +4319,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124364256</v>
+        <v>124364664</v>
       </c>
       <c r="B37" t="n">
-        <v>56722</v>
+        <v>77738</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4319,53 +4331,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100138</v>
+        <v>6487</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490962</v>
+        <v>491024</v>
       </c>
       <c r="R37" t="n">
-        <v>6865124</v>
+        <v>6865165</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 24249-2024 artfynd.xlsx
+++ b/artfynd/A 24249-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124324530</v>
+        <v>124324393</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>78889</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490855</v>
+        <v>490851</v>
       </c>
       <c r="R3" t="n">
-        <v>6864955</v>
+        <v>6864963</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124323716</v>
+        <v>124323971</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>78546</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,21 +904,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,13 +928,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490841</v>
+        <v>490853</v>
       </c>
       <c r="R4" t="n">
-        <v>6865011</v>
+        <v>6865017</v>
       </c>
       <c r="S4" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,19 +978,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124324301</v>
+        <v>124324110</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1030,13 +1030,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490835</v>
+        <v>490853</v>
       </c>
       <c r="R5" t="n">
-        <v>6864998</v>
+        <v>6865011</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,22 +1080,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124323613</v>
+        <v>124324981</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1108,34 +1108,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490844</v>
+        <v>490817</v>
       </c>
       <c r="R6" t="n">
-        <v>6865014</v>
+        <v>6865147</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1305,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124323971</v>
+        <v>124323707</v>
       </c>
       <c r="B8" t="n">
-        <v>78546</v>
+        <v>79892</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1321,21 +1321,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1345,13 +1345,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490853</v>
+        <v>490838</v>
       </c>
       <c r="R8" t="n">
-        <v>6865017</v>
+        <v>6865007</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1395,22 +1395,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124323707</v>
+        <v>124324192</v>
       </c>
       <c r="B9" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1423,21 +1423,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1447,13 +1447,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490838</v>
+        <v>490878</v>
       </c>
       <c r="R9" t="n">
-        <v>6865007</v>
+        <v>6864994</v>
       </c>
       <c r="S9" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1497,19 +1497,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124324167</v>
+        <v>124323908</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1549,13 +1549,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490860</v>
+        <v>490844</v>
       </c>
       <c r="R10" t="n">
-        <v>6864997</v>
+        <v>6864975</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1599,19 +1599,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124323587</v>
+        <v>124324272</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1647,14 +1647,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490850</v>
+        <v>490869</v>
       </c>
       <c r="R11" t="n">
-        <v>6865018</v>
+        <v>6864990</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1713,10 +1713,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124324981</v>
+        <v>124323716</v>
       </c>
       <c r="B12" t="n">
-        <v>79892</v>
+        <v>79891</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1729,21 +1729,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1753,13 +1753,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490817</v>
+        <v>490841</v>
       </c>
       <c r="R12" t="n">
-        <v>6865147</v>
+        <v>6865011</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1803,19 +1803,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124325022</v>
+        <v>124323575</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -1851,17 +1851,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490825</v>
+        <v>490851</v>
       </c>
       <c r="R13" t="n">
-        <v>6865147</v>
+        <v>6865050</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1905,22 +1905,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124324192</v>
+        <v>124325068</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1929,25 +1929,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1957,10 +1957,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490878</v>
+        <v>490832</v>
       </c>
       <c r="R14" t="n">
-        <v>6864994</v>
+        <v>6865135</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1993,6 +1993,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2019,7 +2024,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124324899</v>
+        <v>124323622</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2055,14 +2060,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490800</v>
+        <v>490832</v>
       </c>
       <c r="R15" t="n">
-        <v>6865161</v>
+        <v>6865017</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2109,22 +2114,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124324393</v>
+        <v>124325022</v>
       </c>
       <c r="B16" t="n">
-        <v>78889</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2137,21 +2142,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2161,13 +2166,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490851</v>
+        <v>490825</v>
       </c>
       <c r="R16" t="n">
-        <v>6864963</v>
+        <v>6865147</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2223,7 +2228,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124323622</v>
+        <v>124323587</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2263,13 +2268,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490832</v>
+        <v>490850</v>
       </c>
       <c r="R17" t="n">
-        <v>6865017</v>
+        <v>6865018</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2313,22 +2318,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124323575</v>
+        <v>124323891</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2341,37 +2346,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490851</v>
+        <v>490832</v>
       </c>
       <c r="R18" t="n">
-        <v>6865050</v>
+        <v>6865023</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2401,6 +2406,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2415,12 +2425,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2529,7 +2539,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124324272</v>
+        <v>124324167</v>
       </c>
       <c r="B20" t="n">
         <v>78810</v>
@@ -2569,10 +2579,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490869</v>
+        <v>490860</v>
       </c>
       <c r="R20" t="n">
-        <v>6864990</v>
+        <v>6864997</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2631,7 +2641,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124323908</v>
+        <v>124323613</v>
       </c>
       <c r="B21" t="n">
         <v>78810</v>
@@ -2667,17 +2677,17 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q21" t="n">
         <v>490844</v>
       </c>
       <c r="R21" t="n">
-        <v>6864975</v>
+        <v>6865014</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2721,22 +2731,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124325068</v>
+        <v>124324899</v>
       </c>
       <c r="B22" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2745,25 +2755,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2773,13 +2783,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490832</v>
+        <v>490800</v>
       </c>
       <c r="R22" t="n">
-        <v>6865135</v>
+        <v>6865161</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2809,11 +2819,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-22</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2840,7 +2845,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124324110</v>
+        <v>124324301</v>
       </c>
       <c r="B23" t="n">
         <v>78810</v>
@@ -2880,13 +2885,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490853</v>
+        <v>490835</v>
       </c>
       <c r="R23" t="n">
-        <v>6865011</v>
+        <v>6864998</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2930,22 +2935,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124323891</v>
+        <v>124324530</v>
       </c>
       <c r="B24" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2958,21 +2963,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2982,13 +2987,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490832</v>
+        <v>490855</v>
       </c>
       <c r="R24" t="n">
-        <v>6865023</v>
+        <v>6864955</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3018,11 +3023,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-22</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3049,7 +3049,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124364810</v>
+        <v>124365822</v>
       </c>
       <c r="B25" t="n">
         <v>78810</v>
@@ -3089,10 +3089,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491146</v>
+        <v>490796</v>
       </c>
       <c r="R25" t="n">
-        <v>6865207</v>
+        <v>6865155</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3151,7 +3151,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124365978</v>
+        <v>124364652</v>
       </c>
       <c r="B26" t="n">
         <v>78810</v>
@@ -3187,17 +3187,17 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kullberget, Kullberget, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490934</v>
+        <v>491120</v>
       </c>
       <c r="R26" t="n">
-        <v>6865221</v>
+        <v>6865386</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3224,19 +3224,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>16:07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3251,19 +3241,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124365822</v>
+        <v>124365941</v>
       </c>
       <c r="B27" t="n">
         <v>78810</v>
@@ -3299,14 +3289,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Kullberget, Kullberget, Hls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490796</v>
+        <v>490934</v>
       </c>
       <c r="R27" t="n">
-        <v>6865155</v>
+        <v>6865221</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3336,9 +3326,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3353,19 +3353,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124365206</v>
+        <v>124364496</v>
       </c>
       <c r="B28" t="n">
         <v>78810</v>
@@ -3401,14 +3401,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>491179</v>
+        <v>491193</v>
       </c>
       <c r="R28" t="n">
-        <v>6865114</v>
+        <v>6865330</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3467,7 +3467,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124364538</v>
+        <v>124364810</v>
       </c>
       <c r="B29" t="n">
         <v>78810</v>
@@ -3503,14 +3503,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491166</v>
+        <v>491146</v>
       </c>
       <c r="R29" t="n">
-        <v>6865362</v>
+        <v>6865207</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3569,10 +3569,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124365478</v>
+        <v>124365787</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3585,21 +3585,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3609,13 +3609,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490807</v>
+        <v>490822</v>
       </c>
       <c r="R30" t="n">
-        <v>6865148</v>
+        <v>6865151</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124364652</v>
+        <v>124365478</v>
       </c>
       <c r="B31" t="n">
         <v>78810</v>
@@ -3707,17 +3707,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>491120</v>
+        <v>490807</v>
       </c>
       <c r="R31" t="n">
-        <v>6865386</v>
+        <v>6865148</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124364496</v>
+        <v>124364538</v>
       </c>
       <c r="B32" t="n">
         <v>78810</v>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>491193</v>
+        <v>491166</v>
       </c>
       <c r="R32" t="n">
-        <v>6865330</v>
+        <v>6865362</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3875,10 +3875,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124365787</v>
+        <v>124365206</v>
       </c>
       <c r="B33" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3891,21 +3891,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3915,13 +3915,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490822</v>
+        <v>491179</v>
       </c>
       <c r="R33" t="n">
-        <v>6865151</v>
+        <v>6865114</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>

--- a/artfynd/A 24249-2024 artfynd.xlsx
+++ b/artfynd/A 24249-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124324393</v>
+        <v>124324110</v>
       </c>
       <c r="B3" t="n">
-        <v>78889</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490851</v>
+        <v>490853</v>
       </c>
       <c r="R3" t="n">
-        <v>6864963</v>
+        <v>6865011</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124323971</v>
+        <v>124324393</v>
       </c>
       <c r="B4" t="n">
-        <v>78546</v>
+        <v>78889</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,21 +904,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490853</v>
+        <v>490851</v>
       </c>
       <c r="R4" t="n">
-        <v>6865017</v>
+        <v>6864963</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124324110</v>
+        <v>124323707</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,21 +1006,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,13 +1030,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490853</v>
+        <v>490838</v>
       </c>
       <c r="R5" t="n">
-        <v>6865011</v>
+        <v>6865007</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,22 +1080,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124324981</v>
+        <v>124324272</v>
       </c>
       <c r="B6" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1108,21 +1108,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490817</v>
+        <v>490869</v>
       </c>
       <c r="R6" t="n">
-        <v>6865147</v>
+        <v>6864990</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1194,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124323858</v>
+        <v>124323575</v>
       </c>
       <c r="B7" t="n">
-        <v>91579</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,47 +1206,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490832</v>
+        <v>490851</v>
       </c>
       <c r="R7" t="n">
-        <v>6865023</v>
+        <v>6865050</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1305,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124323707</v>
+        <v>124324192</v>
       </c>
       <c r="B8" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1321,21 +1312,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1345,13 +1336,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490838</v>
+        <v>490878</v>
       </c>
       <c r="R8" t="n">
-        <v>6865007</v>
+        <v>6864994</v>
       </c>
       <c r="S8" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1395,22 +1386,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124324192</v>
+        <v>124323858</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>91579</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1419,41 +1410,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490878</v>
+        <v>490832</v>
       </c>
       <c r="R9" t="n">
-        <v>6864994</v>
+        <v>6865023</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1497,22 +1497,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124323908</v>
+        <v>124323716</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1525,21 +1525,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1549,13 +1549,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490844</v>
+        <v>490841</v>
       </c>
       <c r="R10" t="n">
-        <v>6864975</v>
+        <v>6865011</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1611,10 +1611,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124324272</v>
+        <v>124325068</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1623,25 +1623,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490869</v>
+        <v>490832</v>
       </c>
       <c r="R11" t="n">
-        <v>6864990</v>
+        <v>6865135</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1687,6 +1687,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1713,10 +1718,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124323716</v>
+        <v>124324335</v>
       </c>
       <c r="B12" t="n">
-        <v>79891</v>
+        <v>74901</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1729,21 +1734,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1753,13 +1758,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490841</v>
+        <v>490869</v>
       </c>
       <c r="R12" t="n">
-        <v>6865011</v>
+        <v>6864990</v>
       </c>
       <c r="S12" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1803,19 +1808,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124323575</v>
+        <v>124324530</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -1851,17 +1856,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490851</v>
+        <v>490855</v>
       </c>
       <c r="R13" t="n">
-        <v>6865050</v>
+        <v>6864955</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1905,22 +1910,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124325068</v>
+        <v>124323587</v>
       </c>
       <c r="B14" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1929,38 +1934,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490832</v>
+        <v>490850</v>
       </c>
       <c r="R14" t="n">
-        <v>6865135</v>
+        <v>6865018</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1993,11 +1998,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-22</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2024,10 +2024,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124323622</v>
+        <v>124323971</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2040,37 +2040,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490832</v>
+        <v>490853</v>
       </c>
       <c r="R15" t="n">
         <v>6865017</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2114,19 +2114,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124325022</v>
+        <v>124324899</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490825</v>
+        <v>490800</v>
       </c>
       <c r="R16" t="n">
-        <v>6865147</v>
+        <v>6865161</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2228,7 +2228,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124323587</v>
+        <v>124323613</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490850</v>
+        <v>490844</v>
       </c>
       <c r="R17" t="n">
-        <v>6865018</v>
+        <v>6865014</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2330,10 +2330,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124323891</v>
+        <v>124324167</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2346,21 +2346,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2370,13 +2370,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490832</v>
+        <v>490860</v>
       </c>
       <c r="R18" t="n">
-        <v>6865023</v>
+        <v>6864997</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2406,11 +2406,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-22</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2437,10 +2432,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124324335</v>
+        <v>124325022</v>
       </c>
       <c r="B19" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2453,21 +2448,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2477,13 +2472,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490869</v>
+        <v>490825</v>
       </c>
       <c r="R19" t="n">
-        <v>6864990</v>
+        <v>6865147</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2539,10 +2534,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124324167</v>
+        <v>124324981</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2555,21 +2550,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2579,10 +2574,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490860</v>
+        <v>490817</v>
       </c>
       <c r="R20" t="n">
-        <v>6864997</v>
+        <v>6865147</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2641,7 +2636,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124323613</v>
+        <v>124323622</v>
       </c>
       <c r="B21" t="n">
         <v>78810</v>
@@ -2681,13 +2676,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490844</v>
+        <v>490832</v>
       </c>
       <c r="R21" t="n">
-        <v>6865014</v>
+        <v>6865017</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2731,22 +2726,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124324899</v>
+        <v>124323891</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2759,21 +2754,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2783,10 +2778,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490800</v>
+        <v>490832</v>
       </c>
       <c r="R22" t="n">
-        <v>6865161</v>
+        <v>6865023</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2819,6 +2814,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2845,7 +2845,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124324301</v>
+        <v>124323908</v>
       </c>
       <c r="B23" t="n">
         <v>78810</v>
@@ -2885,13 +2885,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490835</v>
+        <v>490844</v>
       </c>
       <c r="R23" t="n">
-        <v>6864998</v>
+        <v>6864975</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124324530</v>
+        <v>124324301</v>
       </c>
       <c r="B24" t="n">
         <v>78810</v>
@@ -2987,13 +2987,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490855</v>
+        <v>490835</v>
       </c>
       <c r="R24" t="n">
-        <v>6864955</v>
+        <v>6864998</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3037,19 +3037,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124365822</v>
+        <v>124365978</v>
       </c>
       <c r="B25" t="n">
         <v>78810</v>
@@ -3085,14 +3085,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Kullberget, Kullberget, Hls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490796</v>
+        <v>490934</v>
       </c>
       <c r="R25" t="n">
-        <v>6865155</v>
+        <v>6865221</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3122,9 +3122,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3139,19 +3149,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124364652</v>
+        <v>124365822</v>
       </c>
       <c r="B26" t="n">
         <v>78810</v>
@@ -3187,17 +3197,17 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>491120</v>
+        <v>490796</v>
       </c>
       <c r="R26" t="n">
-        <v>6865386</v>
+        <v>6865155</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3253,7 +3263,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124365941</v>
+        <v>124365478</v>
       </c>
       <c r="B27" t="n">
         <v>78810</v>
@@ -3289,14 +3299,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kullberget, Kullberget, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490934</v>
+        <v>490807</v>
       </c>
       <c r="R27" t="n">
-        <v>6865221</v>
+        <v>6865148</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3326,19 +3336,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>16:05</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>16:05</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3353,19 +3353,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124364496</v>
+        <v>124364538</v>
       </c>
       <c r="B28" t="n">
         <v>78810</v>
@@ -3405,10 +3405,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>491193</v>
+        <v>491166</v>
       </c>
       <c r="R28" t="n">
-        <v>6865330</v>
+        <v>6865362</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3467,10 +3467,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124364810</v>
+        <v>124365787</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3483,21 +3483,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491146</v>
+        <v>490822</v>
       </c>
       <c r="R29" t="n">
-        <v>6865207</v>
+        <v>6865151</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3569,10 +3569,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124365787</v>
+        <v>124364496</v>
       </c>
       <c r="B30" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3585,37 +3585,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490822</v>
+        <v>491193</v>
       </c>
       <c r="R30" t="n">
-        <v>6865151</v>
+        <v>6865330</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124365478</v>
+        <v>124364652</v>
       </c>
       <c r="B31" t="n">
         <v>78810</v>
@@ -3707,17 +3707,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490807</v>
+        <v>491120</v>
       </c>
       <c r="R31" t="n">
-        <v>6865148</v>
+        <v>6865386</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124364538</v>
+        <v>124364810</v>
       </c>
       <c r="B32" t="n">
         <v>78810</v>
@@ -3809,14 +3809,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>491166</v>
+        <v>491146</v>
       </c>
       <c r="R32" t="n">
-        <v>6865362</v>
+        <v>6865207</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>

--- a/artfynd/A 24249-2024 artfynd.xlsx
+++ b/artfynd/A 24249-2024 artfynd.xlsx
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124324110</v>
+        <v>124323613</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -822,14 +822,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490853</v>
+        <v>490844</v>
       </c>
       <c r="R3" t="n">
-        <v>6865011</v>
+        <v>6865014</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124324393</v>
+        <v>124323707</v>
       </c>
       <c r="B4" t="n">
-        <v>78889</v>
+        <v>79892</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,21 +904,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,13 +928,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490851</v>
+        <v>490838</v>
       </c>
       <c r="R4" t="n">
-        <v>6864963</v>
+        <v>6865007</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,22 +978,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124323707</v>
+        <v>124323908</v>
       </c>
       <c r="B5" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,21 +1006,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,13 +1030,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490838</v>
+        <v>490844</v>
       </c>
       <c r="R5" t="n">
-        <v>6865007</v>
+        <v>6864975</v>
       </c>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1092,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124324272</v>
+        <v>124324981</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1108,21 +1108,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490869</v>
+        <v>490817</v>
       </c>
       <c r="R6" t="n">
-        <v>6864990</v>
+        <v>6865147</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1194,7 +1194,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124323575</v>
+        <v>124323587</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1234,13 +1234,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490851</v>
+        <v>490850</v>
       </c>
       <c r="R7" t="n">
-        <v>6865050</v>
+        <v>6865018</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1284,19 +1284,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124324192</v>
+        <v>124324530</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490878</v>
+        <v>490855</v>
       </c>
       <c r="R8" t="n">
-        <v>6864994</v>
+        <v>6864955</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1398,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124323858</v>
+        <v>124323716</v>
       </c>
       <c r="B9" t="n">
-        <v>91579</v>
+        <v>79891</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,50 +1410,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490832</v>
+        <v>490841</v>
       </c>
       <c r="R9" t="n">
-        <v>6865023</v>
+        <v>6865011</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1509,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124323716</v>
+        <v>124324110</v>
       </c>
       <c r="B10" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1525,21 +1516,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1549,13 +1540,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490841</v>
+        <v>490853</v>
       </c>
       <c r="R10" t="n">
         <v>6865011</v>
       </c>
       <c r="S10" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1599,22 +1590,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124325068</v>
+        <v>124323971</v>
       </c>
       <c r="B11" t="n">
-        <v>56722</v>
+        <v>78546</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1623,25 +1614,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1651,10 +1642,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490832</v>
+        <v>490853</v>
       </c>
       <c r="R11" t="n">
-        <v>6865135</v>
+        <v>6865017</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1687,11 +1678,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-22</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1718,10 +1704,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124324335</v>
+        <v>124324167</v>
       </c>
       <c r="B12" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1734,21 +1720,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1758,10 +1744,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490869</v>
+        <v>490860</v>
       </c>
       <c r="R12" t="n">
-        <v>6864990</v>
+        <v>6864997</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1820,7 +1806,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124324530</v>
+        <v>124325022</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -1860,13 +1846,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490855</v>
+        <v>490825</v>
       </c>
       <c r="R13" t="n">
-        <v>6864955</v>
+        <v>6865147</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1922,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124323587</v>
+        <v>124325068</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1934,38 +1920,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490850</v>
+        <v>490832</v>
       </c>
       <c r="R14" t="n">
-        <v>6865018</v>
+        <v>6865135</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1998,6 +1984,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2024,10 +2015,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124323971</v>
+        <v>124323858</v>
       </c>
       <c r="B15" t="n">
-        <v>78546</v>
+        <v>91579</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2036,41 +2027,50 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>760</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490853</v>
+        <v>490832</v>
       </c>
       <c r="R15" t="n">
-        <v>6865017</v>
+        <v>6865023</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2114,19 +2114,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124324899</v>
+        <v>124323575</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2162,17 +2162,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490800</v>
+        <v>490851</v>
       </c>
       <c r="R16" t="n">
-        <v>6865161</v>
+        <v>6865050</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2216,19 +2216,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124323613</v>
+        <v>124323622</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2268,13 +2268,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490844</v>
+        <v>490832</v>
       </c>
       <c r="R17" t="n">
-        <v>6865014</v>
+        <v>6865017</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2318,19 +2318,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124324167</v>
+        <v>124324301</v>
       </c>
       <c r="B18" t="n">
         <v>78810</v>
@@ -2370,13 +2370,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490860</v>
+        <v>490835</v>
       </c>
       <c r="R18" t="n">
-        <v>6864997</v>
+        <v>6864998</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2420,19 +2420,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124325022</v>
+        <v>124324899</v>
       </c>
       <c r="B19" t="n">
         <v>78810</v>
@@ -2472,10 +2472,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490825</v>
+        <v>490800</v>
       </c>
       <c r="R19" t="n">
-        <v>6865147</v>
+        <v>6865161</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2534,10 +2534,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124324981</v>
+        <v>124323891</v>
       </c>
       <c r="B20" t="n">
-        <v>79892</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2550,21 +2550,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490817</v>
+        <v>490832</v>
       </c>
       <c r="R20" t="n">
-        <v>6865147</v>
+        <v>6865023</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2610,6 +2610,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2636,7 +2641,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124323622</v>
+        <v>124324272</v>
       </c>
       <c r="B21" t="n">
         <v>78810</v>
@@ -2672,17 +2677,17 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490832</v>
+        <v>490869</v>
       </c>
       <c r="R21" t="n">
-        <v>6865017</v>
+        <v>6864990</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2726,22 +2731,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124323891</v>
+        <v>124324393</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>78889</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2754,21 +2759,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2778,13 +2783,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490832</v>
+        <v>490851</v>
       </c>
       <c r="R22" t="n">
-        <v>6865023</v>
+        <v>6864963</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2814,11 +2819,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-22</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2845,10 +2845,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124323908</v>
+        <v>124324335</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2861,21 +2861,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2885,13 +2885,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490844</v>
+        <v>490869</v>
       </c>
       <c r="R23" t="n">
-        <v>6864975</v>
+        <v>6864990</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2935,19 +2935,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124324301</v>
+        <v>124324192</v>
       </c>
       <c r="B24" t="n">
         <v>78810</v>
@@ -2987,13 +2987,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490835</v>
+        <v>490878</v>
       </c>
       <c r="R24" t="n">
-        <v>6864998</v>
+        <v>6864994</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3037,19 +3037,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124365978</v>
+        <v>124365822</v>
       </c>
       <c r="B25" t="n">
         <v>78810</v>
@@ -3085,14 +3085,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kullberget, Kullberget, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490934</v>
+        <v>490796</v>
       </c>
       <c r="R25" t="n">
-        <v>6865221</v>
+        <v>6865155</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3122,19 +3122,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>16:07</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3149,19 +3139,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124365822</v>
+        <v>124365903</v>
       </c>
       <c r="B26" t="n">
         <v>78810</v>
@@ -3201,10 +3191,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490796</v>
+        <v>490934</v>
       </c>
       <c r="R26" t="n">
-        <v>6865155</v>
+        <v>6865221</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3234,9 +3224,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3251,19 +3251,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124365478</v>
+        <v>124364652</v>
       </c>
       <c r="B27" t="n">
         <v>78810</v>
@@ -3299,17 +3299,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490807</v>
+        <v>491120</v>
       </c>
       <c r="R27" t="n">
-        <v>6865148</v>
+        <v>6865386</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3365,10 +3365,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124364538</v>
+        <v>124365787</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3381,37 +3381,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>491166</v>
+        <v>490822</v>
       </c>
       <c r="R28" t="n">
-        <v>6865362</v>
+        <v>6865151</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3467,10 +3467,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124365787</v>
+        <v>124364538</v>
       </c>
       <c r="B29" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3483,37 +3483,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490822</v>
+        <v>491166</v>
       </c>
       <c r="R29" t="n">
-        <v>6865151</v>
+        <v>6865362</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124364496</v>
+        <v>124365206</v>
       </c>
       <c r="B30" t="n">
         <v>78810</v>
@@ -3605,14 +3605,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>491193</v>
+        <v>491179</v>
       </c>
       <c r="R30" t="n">
-        <v>6865330</v>
+        <v>6865114</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3671,7 +3671,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124364652</v>
+        <v>124364496</v>
       </c>
       <c r="B31" t="n">
         <v>78810</v>
@@ -3711,13 +3711,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>491120</v>
+        <v>491193</v>
       </c>
       <c r="R31" t="n">
-        <v>6865386</v>
+        <v>6865330</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124365206</v>
+        <v>124365478</v>
       </c>
       <c r="B33" t="n">
         <v>78810</v>
@@ -3915,10 +3915,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>491179</v>
+        <v>490807</v>
       </c>
       <c r="R33" t="n">
-        <v>6865114</v>
+        <v>6865148</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4083,10 +4083,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124364917</v>
+        <v>124364664</v>
       </c>
       <c r="B35" t="n">
-        <v>79428</v>
+        <v>77738</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4099,21 +4099,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4123,10 +4123,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>491032</v>
+        <v>491024</v>
       </c>
       <c r="R35" t="n">
-        <v>6865166</v>
+        <v>6865165</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4195,10 +4195,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124364256</v>
+        <v>124364917</v>
       </c>
       <c r="B36" t="n">
-        <v>56722</v>
+        <v>79428</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4207,53 +4207,41 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490962</v>
+        <v>491032</v>
       </c>
       <c r="R36" t="n">
-        <v>6865124</v>
+        <v>6865166</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4282,7 +4270,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4292,7 +4280,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4319,10 +4307,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124364664</v>
+        <v>124364256</v>
       </c>
       <c r="B37" t="n">
-        <v>77738</v>
+        <v>56722</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4331,41 +4319,53 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6487</v>
+        <v>100138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>491024</v>
+        <v>490962</v>
       </c>
       <c r="R37" t="n">
-        <v>6865165</v>
+        <v>6865124</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 24249-2024 artfynd.xlsx
+++ b/artfynd/A 24249-2024 artfynd.xlsx
@@ -3049,7 +3049,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124365822</v>
+        <v>124365978</v>
       </c>
       <c r="B25" t="n">
         <v>78810</v>
@@ -3085,14 +3085,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Kullberget, Kullberget, Hls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490796</v>
+        <v>490934</v>
       </c>
       <c r="R25" t="n">
-        <v>6865155</v>
+        <v>6865221</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3122,9 +3122,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3139,19 +3149,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124365903</v>
+        <v>124364652</v>
       </c>
       <c r="B26" t="n">
         <v>78810</v>
@@ -3187,17 +3197,17 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490934</v>
+        <v>491120</v>
       </c>
       <c r="R26" t="n">
-        <v>6865221</v>
+        <v>6865386</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3224,19 +3234,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>16:02</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>16:02</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3251,19 +3251,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124364652</v>
+        <v>124364538</v>
       </c>
       <c r="B27" t="n">
         <v>78810</v>
@@ -3303,13 +3303,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491120</v>
+        <v>491166</v>
       </c>
       <c r="R27" t="n">
-        <v>6865386</v>
+        <v>6865362</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3365,10 +3365,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124365787</v>
+        <v>124364810</v>
       </c>
       <c r="B28" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3381,21 +3381,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3405,13 +3405,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490822</v>
+        <v>491146</v>
       </c>
       <c r="R28" t="n">
-        <v>6865151</v>
+        <v>6865207</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3467,10 +3467,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124364538</v>
+        <v>124365787</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3483,37 +3483,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491166</v>
+        <v>490822</v>
       </c>
       <c r="R29" t="n">
-        <v>6865362</v>
+        <v>6865151</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124365206</v>
+        <v>124365822</v>
       </c>
       <c r="B30" t="n">
         <v>78810</v>
@@ -3609,10 +3609,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>491179</v>
+        <v>490796</v>
       </c>
       <c r="R30" t="n">
-        <v>6865114</v>
+        <v>6865155</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3773,7 +3773,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124364810</v>
+        <v>124365478</v>
       </c>
       <c r="B32" t="n">
         <v>78810</v>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>491146</v>
+        <v>490807</v>
       </c>
       <c r="R32" t="n">
-        <v>6865207</v>
+        <v>6865148</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3875,7 +3875,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124365478</v>
+        <v>124365206</v>
       </c>
       <c r="B33" t="n">
         <v>78810</v>
@@ -3915,10 +3915,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490807</v>
+        <v>491179</v>
       </c>
       <c r="R33" t="n">
-        <v>6865148</v>
+        <v>6865114</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4083,10 +4083,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124364664</v>
+        <v>124364917</v>
       </c>
       <c r="B35" t="n">
-        <v>77738</v>
+        <v>79428</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4099,21 +4099,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4123,10 +4123,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>491024</v>
+        <v>491032</v>
       </c>
       <c r="R35" t="n">
-        <v>6865165</v>
+        <v>6865166</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4195,10 +4195,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124364917</v>
+        <v>124364664</v>
       </c>
       <c r="B36" t="n">
-        <v>79428</v>
+        <v>77738</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4211,21 +4211,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4235,10 +4235,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>491032</v>
+        <v>491024</v>
       </c>
       <c r="R36" t="n">
-        <v>6865166</v>
+        <v>6865165</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4270,7 +4270,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 24249-2024 artfynd.xlsx
+++ b/artfynd/A 24249-2024 artfynd.xlsx
@@ -4083,10 +4083,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124364917</v>
+        <v>124364664</v>
       </c>
       <c r="B35" t="n">
-        <v>79428</v>
+        <v>77738</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4099,21 +4099,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4123,10 +4123,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>491032</v>
+        <v>491024</v>
       </c>
       <c r="R35" t="n">
-        <v>6865166</v>
+        <v>6865165</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4195,10 +4195,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124364664</v>
+        <v>124364256</v>
       </c>
       <c r="B36" t="n">
-        <v>77738</v>
+        <v>56722</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4207,41 +4207,53 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6487</v>
+        <v>100138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>491024</v>
+        <v>490962</v>
       </c>
       <c r="R36" t="n">
-        <v>6865165</v>
+        <v>6865124</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4270,7 +4282,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4280,7 +4292,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4307,10 +4319,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124364256</v>
+        <v>124364917</v>
       </c>
       <c r="B37" t="n">
-        <v>56722</v>
+        <v>79428</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4319,53 +4331,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490962</v>
+        <v>491032</v>
       </c>
       <c r="R37" t="n">
-        <v>6865124</v>
+        <v>6865166</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 24249-2024 artfynd.xlsx
+++ b/artfynd/A 24249-2024 artfynd.xlsx
@@ -4083,10 +4083,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124364664</v>
+        <v>124364917</v>
       </c>
       <c r="B35" t="n">
-        <v>77738</v>
+        <v>79428</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4099,21 +4099,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4123,10 +4123,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>491024</v>
+        <v>491032</v>
       </c>
       <c r="R35" t="n">
-        <v>6865165</v>
+        <v>6865166</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4319,10 +4319,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124364917</v>
+        <v>124364664</v>
       </c>
       <c r="B37" t="n">
-        <v>79428</v>
+        <v>77738</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4335,21 +4335,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4359,10 +4359,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>491032</v>
+        <v>491024</v>
       </c>
       <c r="R37" t="n">
-        <v>6865166</v>
+        <v>6865165</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4394,7 +4394,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 24249-2024 artfynd.xlsx
+++ b/artfynd/A 24249-2024 artfynd.xlsx
@@ -4083,10 +4083,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124364917</v>
+        <v>124364256</v>
       </c>
       <c r="B35" t="n">
-        <v>79428</v>
+        <v>56722</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4095,41 +4095,53 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>491032</v>
+        <v>490962</v>
       </c>
       <c r="R35" t="n">
-        <v>6865166</v>
+        <v>6865124</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4158,7 +4170,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4168,7 +4180,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4195,10 +4207,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124364256</v>
+        <v>124364917</v>
       </c>
       <c r="B36" t="n">
-        <v>56722</v>
+        <v>79428</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4207,53 +4219,41 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490962</v>
+        <v>491032</v>
       </c>
       <c r="R36" t="n">
-        <v>6865124</v>
+        <v>6865166</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 24249-2024 artfynd.xlsx
+++ b/artfynd/A 24249-2024 artfynd.xlsx
@@ -4083,10 +4083,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124364256</v>
+        <v>124364917</v>
       </c>
       <c r="B35" t="n">
-        <v>56722</v>
+        <v>79565</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4095,53 +4095,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490962</v>
+        <v>491032</v>
       </c>
       <c r="R35" t="n">
-        <v>6865124</v>
+        <v>6865166</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4170,7 +4158,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4180,7 +4168,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4207,10 +4195,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124364917</v>
+        <v>124364664</v>
       </c>
       <c r="B36" t="n">
-        <v>79428</v>
+        <v>77874</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4223,21 +4211,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4247,10 +4235,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>491032</v>
+        <v>491024</v>
       </c>
       <c r="R36" t="n">
-        <v>6865166</v>
+        <v>6865165</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4282,7 +4270,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4292,7 +4280,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4319,10 +4307,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124364664</v>
+        <v>124364256</v>
       </c>
       <c r="B37" t="n">
-        <v>77738</v>
+        <v>56836</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4331,41 +4319,53 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6487</v>
+        <v>100138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>491024</v>
+        <v>490962</v>
       </c>
       <c r="R37" t="n">
-        <v>6865165</v>
+        <v>6865124</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 24249-2024 artfynd.xlsx
+++ b/artfynd/A 24249-2024 artfynd.xlsx
@@ -4195,10 +4195,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124364664</v>
+        <v>124364256</v>
       </c>
       <c r="B36" t="n">
-        <v>77874</v>
+        <v>56836</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4207,41 +4207,53 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6487</v>
+        <v>100138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>491024</v>
+        <v>490962</v>
       </c>
       <c r="R36" t="n">
-        <v>6865165</v>
+        <v>6865124</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4270,7 +4282,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4280,7 +4292,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4307,10 +4319,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124364256</v>
+        <v>124364664</v>
       </c>
       <c r="B37" t="n">
-        <v>56836</v>
+        <v>77874</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4319,53 +4331,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100138</v>
+        <v>6487</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490962</v>
+        <v>491024</v>
       </c>
       <c r="R37" t="n">
-        <v>6865124</v>
+        <v>6865165</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 24249-2024 artfynd.xlsx
+++ b/artfynd/A 24249-2024 artfynd.xlsx
@@ -4083,10 +4083,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124364917</v>
+        <v>124364256</v>
       </c>
       <c r="B35" t="n">
-        <v>79565</v>
+        <v>56836</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4095,41 +4095,53 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>491032</v>
+        <v>490962</v>
       </c>
       <c r="R35" t="n">
-        <v>6865166</v>
+        <v>6865124</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4158,7 +4170,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4168,7 +4180,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4195,10 +4207,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124364256</v>
+        <v>124364664</v>
       </c>
       <c r="B36" t="n">
-        <v>56836</v>
+        <v>77874</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4207,53 +4219,41 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100138</v>
+        <v>6487</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490962</v>
+        <v>491024</v>
       </c>
       <c r="R36" t="n">
-        <v>6865124</v>
+        <v>6865165</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4319,10 +4319,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124364664</v>
+        <v>124364917</v>
       </c>
       <c r="B37" t="n">
-        <v>77874</v>
+        <v>79565</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4335,21 +4335,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4359,10 +4359,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>491024</v>
+        <v>491032</v>
       </c>
       <c r="R37" t="n">
-        <v>6865165</v>
+        <v>6865166</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4394,7 +4394,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 24249-2024 artfynd.xlsx
+++ b/artfynd/A 24249-2024 artfynd.xlsx
@@ -4088,11 +4088,6 @@
       <c r="B35" t="n">
         <v>56836</v>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D35" t="inlineStr">
         <is>
           <t>LC</t>
@@ -4212,11 +4207,6 @@
       <c r="B36" t="n">
         <v>77874</v>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D36" t="inlineStr">
         <is>
           <t>NT</t>
@@ -4323,11 +4313,6 @@
       </c>
       <c r="B37" t="n">
         <v>79565</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 24249-2024 artfynd.xlsx
+++ b/artfynd/A 24249-2024 artfynd.xlsx
@@ -2537,7 +2537,7 @@
         <v>124323891</v>
       </c>
       <c r="B20" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 24249-2024 artfynd.xlsx
+++ b/artfynd/A 24249-2024 artfynd.xlsx
@@ -2537,7 +2537,7 @@
         <v>124323891</v>
       </c>
       <c r="B20" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 24249-2024 artfynd.xlsx
+++ b/artfynd/A 24249-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118676083</v>
+        <v>124323858</v>
       </c>
       <c r="B2" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Öjingsvallen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490841</v>
+        <v>490832</v>
       </c>
       <c r="R2" t="n">
-        <v>6865035</v>
+        <v>6865023</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,17 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,27 +769,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124323613</v>
+        <v>124324393</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,34 +792,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490844</v>
+        <v>490851</v>
       </c>
       <c r="R3" t="n">
-        <v>6865014</v>
+        <v>6864963</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -891,12 +881,7 @@
         <v>124323707</v>
       </c>
       <c r="B4" t="n">
-        <v>79892</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -990,15 +975,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124323908</v>
+        <v>124324981</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1006,21 +986,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,13 +1010,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490844</v>
+        <v>490817</v>
       </c>
       <c r="R5" t="n">
-        <v>6864975</v>
+        <v>6865147</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,27 +1060,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124324981</v>
+        <v>124365787</v>
       </c>
       <c r="B6" t="n">
-        <v>79892</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1132,13 +1107,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490817</v>
+        <v>490822</v>
       </c>
       <c r="R6" t="n">
-        <v>6865147</v>
+        <v>6865151</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1162,12 +1137,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1182,31 +1157,26 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124323587</v>
+        <v>118676083</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1227,20 +1197,24 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Öjingsvallen, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490850</v>
+        <v>490841</v>
       </c>
       <c r="R7" t="n">
-        <v>6865018</v>
+        <v>6865035</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1264,12 +1238,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2024-06-05</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1284,31 +1263,26 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124324530</v>
+        <v>124323575</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1332,17 +1306,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490855</v>
+        <v>490851</v>
       </c>
       <c r="R8" t="n">
-        <v>6864955</v>
+        <v>6865050</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1386,65 +1360,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124323716</v>
+        <v>124323587</v>
       </c>
       <c r="B9" t="n">
-        <v>79891</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490841</v>
+        <v>490850</v>
       </c>
       <c r="R9" t="n">
-        <v>6865011</v>
+        <v>6865018</v>
       </c>
       <c r="S9" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1488,31 +1457,26 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124324110</v>
+        <v>124323613</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1536,14 +1500,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490853</v>
+        <v>490844</v>
       </c>
       <c r="R10" t="n">
-        <v>6865011</v>
+        <v>6865014</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1602,53 +1566,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124323971</v>
+        <v>124323622</v>
       </c>
       <c r="B11" t="n">
-        <v>78546</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490853</v>
+        <v>490832</v>
       </c>
       <c r="R11" t="n">
         <v>6865017</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1692,31 +1651,26 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124324167</v>
+        <v>124323908</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1744,13 +1698,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490860</v>
+        <v>490844</v>
       </c>
       <c r="R12" t="n">
-        <v>6864997</v>
+        <v>6864975</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1794,31 +1748,26 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124325022</v>
+        <v>124324110</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1846,13 +1795,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490825</v>
+        <v>490853</v>
       </c>
       <c r="R13" t="n">
-        <v>6865147</v>
+        <v>6865011</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1908,37 +1857,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124325068</v>
+        <v>124324167</v>
       </c>
       <c r="B14" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1948,10 +1892,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490832</v>
+        <v>490860</v>
       </c>
       <c r="R14" t="n">
-        <v>6865135</v>
+        <v>6864997</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1984,11 +1928,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-22</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2015,15 +1954,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124323858</v>
+        <v>124324192</v>
       </c>
       <c r="B15" t="n">
-        <v>91579</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2031,46 +1965,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490832</v>
+        <v>490878</v>
       </c>
       <c r="R15" t="n">
-        <v>6865023</v>
+        <v>6864994</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2114,31 +2039,26 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124323575</v>
+        <v>124324272</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2162,17 +2082,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490851</v>
+        <v>490869</v>
       </c>
       <c r="R16" t="n">
-        <v>6865050</v>
+        <v>6864990</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2216,31 +2136,26 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124323622</v>
+        <v>124324301</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2264,14 +2179,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490832</v>
+        <v>490835</v>
       </c>
       <c r="R17" t="n">
-        <v>6865017</v>
+        <v>6864998</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2330,19 +2245,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124324301</v>
+        <v>124324530</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2370,13 +2280,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490835</v>
+        <v>490855</v>
       </c>
       <c r="R18" t="n">
-        <v>6864998</v>
+        <v>6864955</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2420,12 +2330,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2435,16 +2345,11 @@
         <v>124324899</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2534,32 +2439,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124323891</v>
+        <v>124325022</v>
       </c>
       <c r="B20" t="n">
-        <v>57852</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2569,10 +2474,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490832</v>
+        <v>490825</v>
       </c>
       <c r="R20" t="n">
-        <v>6865023</v>
+        <v>6865147</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2605,11 +2510,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-22</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2636,19 +2536,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124324272</v>
+        <v>124364496</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2672,17 +2567,17 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490869</v>
+        <v>491193</v>
       </c>
       <c r="R21" t="n">
-        <v>6864990</v>
+        <v>6865330</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2706,12 +2601,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2726,65 +2621,60 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124324393</v>
+        <v>124364538</v>
       </c>
       <c r="B22" t="n">
-        <v>78889</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490851</v>
+        <v>491166</v>
       </c>
       <c r="R22" t="n">
-        <v>6864963</v>
+        <v>6865362</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2808,12 +2698,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2828,65 +2718,60 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124324335</v>
+        <v>124364652</v>
       </c>
       <c r="B23" t="n">
-        <v>74901</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490869</v>
+        <v>491120</v>
       </c>
       <c r="R23" t="n">
-        <v>6864990</v>
+        <v>6865386</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2910,12 +2795,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2930,31 +2815,26 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124324192</v>
+        <v>124364810</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -2982,13 +2862,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490878</v>
+        <v>491146</v>
       </c>
       <c r="R24" t="n">
-        <v>6864994</v>
+        <v>6865207</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3012,12 +2892,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3032,31 +2912,26 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124365978</v>
+        <v>124365206</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3080,14 +2955,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kullberget, Kullberget, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490934</v>
+        <v>491179</v>
       </c>
       <c r="R25" t="n">
-        <v>6865221</v>
+        <v>6865114</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3117,19 +2992,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>16:07</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3144,31 +3009,26 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124364652</v>
+        <v>124365478</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3192,17 +3052,17 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>491120</v>
+        <v>490807</v>
       </c>
       <c r="R26" t="n">
-        <v>6865386</v>
+        <v>6865148</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3258,19 +3118,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124364538</v>
+        <v>124365822</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3294,14 +3149,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491166</v>
+        <v>490796</v>
       </c>
       <c r="R27" t="n">
-        <v>6865362</v>
+        <v>6865155</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3360,19 +3215,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124364810</v>
+        <v>124365903</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3400,10 +3250,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>491146</v>
+        <v>490934</v>
       </c>
       <c r="R28" t="n">
-        <v>6865207</v>
+        <v>6865221</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3433,9 +3283,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3450,65 +3310,63 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124365787</v>
+        <v>124381335</v>
       </c>
       <c r="B29" t="n">
-        <v>79892</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Fågelsjö, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490822</v>
+        <v>491025</v>
       </c>
       <c r="R29" t="n">
-        <v>6865151</v>
+        <v>6865146</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3546,33 +3404,29 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124365822</v>
+        <v>124324335</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3580,21 +3434,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3604,13 +3458,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490796</v>
+        <v>490869</v>
       </c>
       <c r="R30" t="n">
-        <v>6865155</v>
+        <v>6864990</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3634,12 +3488,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3654,27 +3508,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124364496</v>
+        <v>124323971</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3682,37 +3531,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>491193</v>
+        <v>490853</v>
       </c>
       <c r="R31" t="n">
-        <v>6865330</v>
+        <v>6865017</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3736,12 +3585,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3756,27 +3605,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124365478</v>
+        <v>124364917</v>
       </c>
       <c r="B32" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3784,21 +3628,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3808,10 +3652,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490807</v>
+        <v>491032</v>
       </c>
       <c r="R32" t="n">
-        <v>6865148</v>
+        <v>6865166</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3841,9 +3685,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3858,27 +3712,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124365206</v>
+        <v>124323716</v>
       </c>
       <c r="B33" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3886,21 +3735,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3910,13 +3759,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>491179</v>
+        <v>490841</v>
       </c>
       <c r="R33" t="n">
-        <v>6865114</v>
+        <v>6865011</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3940,12 +3789,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3972,15 +3821,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124381335</v>
+        <v>124364664</v>
       </c>
       <c r="B34" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78334</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3988,40 +3832,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>491025</v>
+        <v>491024</v>
       </c>
       <c r="R34" t="n">
-        <v>6865146</v>
+        <v>6865165</v>
       </c>
       <c r="S34" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4048,87 +3889,84 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124364256</v>
+        <v>124323891</v>
       </c>
       <c r="B35" t="n">
-        <v>56836</v>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490962</v>
+        <v>490832</v>
       </c>
       <c r="R35" t="n">
-        <v>6865124</v>
+        <v>6865023</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4155,22 +3993,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>15:16</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>15:16</t>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4185,44 +4018,44 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124364664</v>
+        <v>124325068</v>
       </c>
       <c r="B36" t="n">
-        <v>77874</v>
+        <v>57141</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6487</v>
+        <v>100138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4232,13 +4065,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>491024</v>
+        <v>490832</v>
       </c>
       <c r="R36" t="n">
-        <v>6865165</v>
+        <v>6865135</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4262,22 +4095,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>15:28</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>15:28</t>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4292,60 +4120,72 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124364917</v>
+        <v>124364256</v>
       </c>
       <c r="B37" t="n">
-        <v>79565</v>
+        <v>57141</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>491032</v>
+        <v>490962</v>
       </c>
       <c r="R37" t="n">
-        <v>6865166</v>
+        <v>6865124</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4374,7 +4214,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4384,7 +4224,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4408,6 +4248,103 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>124364790</v>
+      </c>
+      <c r="B38" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Kullvallen, Kullvallen, Hls</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>491141</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6865216</v>
+      </c>
+      <c r="S38" t="n">
+        <v>15</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Ängersjö</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24249-2024 artfynd.xlsx
+++ b/artfynd/A 24249-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AZ38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124323858</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124324393</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124323707</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1069,6 +1089,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124324981</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1166,6 +1191,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124365787</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1272,6 +1302,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118676083</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1369,6 +1404,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124323575</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1466,6 +1506,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124323587</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1563,6 +1608,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124323613</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1660,6 +1710,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124323622</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1757,6 +1812,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124323908</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1854,6 +1914,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124324110</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1951,6 +2016,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124324167</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2048,6 +2118,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124324192</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2145,6 +2220,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124324272</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2242,6 +2322,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124324301</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2339,6 +2424,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124324530</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2436,6 +2526,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124324899</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2533,6 +2628,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124325022</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2630,6 +2730,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124364496</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2727,6 +2832,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124364538</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2824,6 +2934,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124364652</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2921,6 +3036,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124364810</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3018,6 +3138,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124365206</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3115,6 +3240,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124365478</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3212,6 +3342,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124365822</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3319,6 +3454,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124365903</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3420,6 +3560,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124381335</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3517,6 +3662,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124324335</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3614,6 +3764,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124323971</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3721,6 +3876,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124364917</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3818,6 +3978,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124323716</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3925,6 +4090,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124364664</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4027,6 +4197,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124323891</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4129,6 +4304,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124325068</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4248,6 +4428,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124364256</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4345,8 +4530,52 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124364790</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 24249-2024 artfynd.xlsx
+++ b/artfynd/A 24249-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ38"/>
+  <dimension ref="A1:AZ42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,57 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124323858</v>
+        <v>135900796</v>
       </c>
       <c r="B2" t="n">
-        <v>92509</v>
+        <v>79473</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>760</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490832</v>
+        <v>490840</v>
       </c>
       <c r="R2" t="n">
-        <v>6865023</v>
+        <v>6865030</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,12 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,27 +775,27 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson, Malte Lindberg, Emilia Blixt, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124323858</t>
+          <t>https://artportalen.se/Sighting/135900796</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124324393</v>
+        <v>135900859</v>
       </c>
       <c r="B3" t="n">
-        <v>79406</v>
+        <v>79473</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,37 +803,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>864</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490851</v>
+        <v>490779</v>
       </c>
       <c r="R3" t="n">
-        <v>6864963</v>
+        <v>6865018</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -856,12 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -876,65 +887,74 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson, Tilde Carlinger, Malte Lindberg, Emilia Blixt</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124324393</t>
+          <t>https://artportalen.se/Sighting/135900859</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124323707</v>
+        <v>124323858</v>
       </c>
       <c r="B4" t="n">
-        <v>80433</v>
+        <v>92509</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>760</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490838</v>
+        <v>490832</v>
       </c>
       <c r="R4" t="n">
-        <v>6865007</v>
+        <v>6865023</v>
       </c>
       <c r="S4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,16 +1009,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124323707</t>
+          <t>https://artportalen.se/Sighting/124323858</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124324981</v>
+        <v>124324393</v>
       </c>
       <c r="B5" t="n">
-        <v>80433</v>
+        <v>79406</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1006,21 +1026,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490817</v>
+        <v>490851</v>
       </c>
       <c r="R5" t="n">
-        <v>6865147</v>
+        <v>6864963</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1091,13 +1111,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124324981</t>
+          <t>https://artportalen.se/Sighting/124324393</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124365787</v>
+        <v>124323707</v>
       </c>
       <c r="B6" t="n">
         <v>80433</v>
@@ -1132,13 +1152,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490822</v>
+        <v>490838</v>
       </c>
       <c r="R6" t="n">
-        <v>6865151</v>
+        <v>6865007</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1162,12 +1182,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,58 +1213,54 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124365787</t>
+          <t>https://artportalen.se/Sighting/124323707</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118676083</v>
+        <v>124324981</v>
       </c>
       <c r="B7" t="n">
-        <v>79327</v>
+        <v>80433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Öjingsvallen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490841</v>
+        <v>490817</v>
       </c>
       <c r="R7" t="n">
-        <v>6865035</v>
+        <v>6865147</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1268,17 +1284,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1293,65 +1304,65 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118676083</t>
+          <t>https://artportalen.se/Sighting/124324981</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124323575</v>
+        <v>124365787</v>
       </c>
       <c r="B8" t="n">
-        <v>79327</v>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490851</v>
+        <v>490822</v>
       </c>
       <c r="R8" t="n">
-        <v>6865050</v>
+        <v>6865151</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1375,12 +1386,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1406,54 +1417,54 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124323575</t>
+          <t>https://artportalen.se/Sighting/124365787</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124323587</v>
+        <v>135900799</v>
       </c>
       <c r="B9" t="n">
-        <v>79327</v>
+        <v>80557</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490850</v>
+        <v>490843</v>
       </c>
       <c r="R9" t="n">
-        <v>6865018</v>
+        <v>6865011</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1477,12 +1488,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1497,24 +1518,24 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson, Malte Lindberg, Emilia Blixt, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124323587</t>
+          <t>https://artportalen.se/Sighting/135900799</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124323613</v>
+        <v>118676083</v>
       </c>
       <c r="B10" t="n">
         <v>79327</v>
@@ -1542,20 +1563,24 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Öjingsvallen, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490844</v>
+        <v>490841</v>
       </c>
       <c r="R10" t="n">
-        <v>6865014</v>
+        <v>6865035</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1579,12 +1604,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2024-06-05</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1599,24 +1629,24 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124323613</t>
+          <t>https://artportalen.se/Sighting/118676083</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124323622</v>
+        <v>124323575</v>
       </c>
       <c r="B11" t="n">
         <v>79327</v>
@@ -1651,13 +1681,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490832</v>
+        <v>490851</v>
       </c>
       <c r="R11" t="n">
-        <v>6865017</v>
+        <v>6865050</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1712,13 +1742,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124323622</t>
+          <t>https://artportalen.se/Sighting/124323575</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124323908</v>
+        <v>124323587</v>
       </c>
       <c r="B12" t="n">
         <v>79327</v>
@@ -1749,17 +1779,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490844</v>
+        <v>490850</v>
       </c>
       <c r="R12" t="n">
-        <v>6864975</v>
+        <v>6865018</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1803,24 +1833,24 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124323908</t>
+          <t>https://artportalen.se/Sighting/124323587</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124324110</v>
+        <v>124323613</v>
       </c>
       <c r="B13" t="n">
         <v>79327</v>
@@ -1851,14 +1881,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490853</v>
+        <v>490844</v>
       </c>
       <c r="R13" t="n">
-        <v>6865011</v>
+        <v>6865014</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1916,13 +1946,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124324110</t>
+          <t>https://artportalen.se/Sighting/124323613</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124324167</v>
+        <v>124323622</v>
       </c>
       <c r="B14" t="n">
         <v>79327</v>
@@ -1953,17 +1983,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490860</v>
+        <v>490832</v>
       </c>
       <c r="R14" t="n">
-        <v>6864997</v>
+        <v>6865017</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2007,24 +2037,24 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124324167</t>
+          <t>https://artportalen.se/Sighting/124323622</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124324192</v>
+        <v>124323908</v>
       </c>
       <c r="B15" t="n">
         <v>79327</v>
@@ -2059,13 +2089,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490878</v>
+        <v>490844</v>
       </c>
       <c r="R15" t="n">
-        <v>6864994</v>
+        <v>6864975</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2109,24 +2139,24 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124324192</t>
+          <t>https://artportalen.se/Sighting/124323908</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124324272</v>
+        <v>124324110</v>
       </c>
       <c r="B16" t="n">
         <v>79327</v>
@@ -2161,10 +2191,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490869</v>
+        <v>490853</v>
       </c>
       <c r="R16" t="n">
-        <v>6864990</v>
+        <v>6865011</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2222,13 +2252,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124324272</t>
+          <t>https://artportalen.se/Sighting/124324110</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124324301</v>
+        <v>124324167</v>
       </c>
       <c r="B17" t="n">
         <v>79327</v>
@@ -2263,13 +2293,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490835</v>
+        <v>490860</v>
       </c>
       <c r="R17" t="n">
-        <v>6864998</v>
+        <v>6864997</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2313,24 +2343,24 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124324301</t>
+          <t>https://artportalen.se/Sighting/124324167</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124324530</v>
+        <v>124324192</v>
       </c>
       <c r="B18" t="n">
         <v>79327</v>
@@ -2365,10 +2395,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490855</v>
+        <v>490878</v>
       </c>
       <c r="R18" t="n">
-        <v>6864955</v>
+        <v>6864994</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2426,13 +2456,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124324530</t>
+          <t>https://artportalen.se/Sighting/124324192</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124324899</v>
+        <v>124324272</v>
       </c>
       <c r="B19" t="n">
         <v>79327</v>
@@ -2467,13 +2497,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490800</v>
+        <v>490869</v>
       </c>
       <c r="R19" t="n">
-        <v>6865161</v>
+        <v>6864990</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2528,13 +2558,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124324899</t>
+          <t>https://artportalen.se/Sighting/124324272</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124325022</v>
+        <v>124324301</v>
       </c>
       <c r="B20" t="n">
         <v>79327</v>
@@ -2569,10 +2599,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490825</v>
+        <v>490835</v>
       </c>
       <c r="R20" t="n">
-        <v>6865147</v>
+        <v>6864998</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2619,24 +2649,24 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124325022</t>
+          <t>https://artportalen.se/Sighting/124324301</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124364496</v>
+        <v>124324530</v>
       </c>
       <c r="B21" t="n">
         <v>79327</v>
@@ -2667,17 +2697,17 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>491193</v>
+        <v>490855</v>
       </c>
       <c r="R21" t="n">
-        <v>6865330</v>
+        <v>6864955</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2701,12 +2731,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2721,24 +2751,24 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124364496</t>
+          <t>https://artportalen.se/Sighting/124324530</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124364538</v>
+        <v>124324899</v>
       </c>
       <c r="B22" t="n">
         <v>79327</v>
@@ -2769,17 +2799,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>491166</v>
+        <v>490800</v>
       </c>
       <c r="R22" t="n">
-        <v>6865362</v>
+        <v>6865161</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2803,12 +2833,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2823,24 +2853,24 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124364538</t>
+          <t>https://artportalen.se/Sighting/124324899</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124364652</v>
+        <v>124325022</v>
       </c>
       <c r="B23" t="n">
         <v>79327</v>
@@ -2871,14 +2901,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491120</v>
+        <v>490825</v>
       </c>
       <c r="R23" t="n">
-        <v>6865386</v>
+        <v>6865147</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2905,12 +2935,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2925,24 +2955,24 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124364652</t>
+          <t>https://artportalen.se/Sighting/124325022</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124364810</v>
+        <v>124364496</v>
       </c>
       <c r="B24" t="n">
         <v>79327</v>
@@ -2973,14 +3003,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491146</v>
+        <v>491193</v>
       </c>
       <c r="R24" t="n">
-        <v>6865207</v>
+        <v>6865330</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3038,13 +3068,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124364810</t>
+          <t>https://artportalen.se/Sighting/124364496</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124365206</v>
+        <v>124364538</v>
       </c>
       <c r="B25" t="n">
         <v>79327</v>
@@ -3075,14 +3105,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491179</v>
+        <v>491166</v>
       </c>
       <c r="R25" t="n">
-        <v>6865114</v>
+        <v>6865362</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3140,13 +3170,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124365206</t>
+          <t>https://artportalen.se/Sighting/124364538</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124365478</v>
+        <v>124364652</v>
       </c>
       <c r="B26" t="n">
         <v>79327</v>
@@ -3177,17 +3207,17 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490807</v>
+        <v>491120</v>
       </c>
       <c r="R26" t="n">
-        <v>6865148</v>
+        <v>6865386</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3242,13 +3272,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124365478</t>
+          <t>https://artportalen.se/Sighting/124364652</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124365822</v>
+        <v>124364810</v>
       </c>
       <c r="B27" t="n">
         <v>79327</v>
@@ -3283,10 +3313,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490796</v>
+        <v>491146</v>
       </c>
       <c r="R27" t="n">
-        <v>6865155</v>
+        <v>6865207</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3344,13 +3374,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124365822</t>
+          <t>https://artportalen.se/Sighting/124364810</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124365903</v>
+        <v>124365206</v>
       </c>
       <c r="B28" t="n">
         <v>79327</v>
@@ -3385,10 +3415,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490934</v>
+        <v>491179</v>
       </c>
       <c r="R28" t="n">
-        <v>6865221</v>
+        <v>6865114</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3418,19 +3448,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>16:02</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>16:02</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3445,24 +3465,24 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124365903</t>
+          <t>https://artportalen.se/Sighting/124365206</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124381335</v>
+        <v>124365478</v>
       </c>
       <c r="B29" t="n">
         <v>79327</v>
@@ -3491,22 +3511,19 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491025</v>
+        <v>490807</v>
       </c>
       <c r="R29" t="n">
-        <v>6865146</v>
+        <v>6865148</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3544,56 +3561,55 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124381335</t>
+          <t>https://artportalen.se/Sighting/124365478</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124324335</v>
+        <v>124365822</v>
       </c>
       <c r="B30" t="n">
-        <v>83307</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3603,13 +3619,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490869</v>
+        <v>490796</v>
       </c>
       <c r="R30" t="n">
-        <v>6864990</v>
+        <v>6865155</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3633,12 +3649,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3653,49 +3669,49 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124324335</t>
+          <t>https://artportalen.se/Sighting/124365822</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124323971</v>
+        <v>124365903</v>
       </c>
       <c r="B31" t="n">
-        <v>79084</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3705,13 +3721,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490853</v>
+        <v>490934</v>
       </c>
       <c r="R31" t="n">
-        <v>6865017</v>
+        <v>6865221</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3735,12 +3751,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3755,65 +3781,68 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124323971</t>
+          <t>https://artportalen.se/Sighting/124365903</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124364917</v>
+        <v>124381335</v>
       </c>
       <c r="B32" t="n">
-        <v>79946</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Fågelsjö, Hls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>491032</v>
+        <v>491025</v>
       </c>
       <c r="R32" t="n">
-        <v>6865166</v>
+        <v>6865146</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3840,54 +3869,45 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124364917</t>
+          <t>https://artportalen.se/Sighting/124381335</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124323716</v>
+        <v>124324335</v>
       </c>
       <c r="B33" t="n">
-        <v>80432</v>
+        <v>83307</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3895,21 +3915,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3919,13 +3939,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490841</v>
+        <v>490869</v>
       </c>
       <c r="R33" t="n">
-        <v>6865011</v>
+        <v>6864990</v>
       </c>
       <c r="S33" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3969,27 +3989,27 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124323716</t>
+          <t>https://artportalen.se/Sighting/124324335</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124364664</v>
+        <v>124323971</v>
       </c>
       <c r="B34" t="n">
-        <v>78334</v>
+        <v>79084</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3997,21 +4017,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4021,13 +4041,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>491024</v>
+        <v>490853</v>
       </c>
       <c r="R34" t="n">
-        <v>6865165</v>
+        <v>6865017</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4051,22 +4071,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>15:28</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>15:28</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4081,27 +4091,27 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124364664</t>
+          <t>https://artportalen.se/Sighting/124323971</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124323891</v>
+        <v>124364917</v>
       </c>
       <c r="B35" t="n">
-        <v>57953</v>
+        <v>79946</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4109,21 +4119,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4133,13 +4143,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490832</v>
+        <v>491032</v>
       </c>
       <c r="R35" t="n">
-        <v>6865023</v>
+        <v>6865166</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4163,17 +4173,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4188,49 +4203,49 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124323891</t>
+          <t>https://artportalen.se/Sighting/124364917</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124325068</v>
+        <v>124323716</v>
       </c>
       <c r="B36" t="n">
-        <v>57141</v>
+        <v>80432</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4240,13 +4255,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490832</v>
+        <v>490841</v>
       </c>
       <c r="R36" t="n">
-        <v>6865135</v>
+        <v>6865011</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4276,11 +4291,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-04-22</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4295,77 +4305,65 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124325068</t>
+          <t>https://artportalen.se/Sighting/124323716</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124364256</v>
+        <v>135900798</v>
       </c>
       <c r="B37" t="n">
-        <v>57141</v>
+        <v>80556</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490962</v>
+        <v>490842</v>
       </c>
       <c r="R37" t="n">
-        <v>6865124</v>
+        <v>6865012</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4389,22 +4387,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4419,27 +4417,27 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson, Malte Lindberg, Emilia Blixt, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124364256</t>
+          <t>https://artportalen.se/Sighting/135900798</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124364790</v>
+        <v>124364664</v>
       </c>
       <c r="B38" t="n">
-        <v>58114</v>
+        <v>78334</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4447,21 +4445,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>6487</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4471,10 +4469,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491141</v>
+        <v>491024</v>
       </c>
       <c r="R38" t="n">
-        <v>6865216</v>
+        <v>6865165</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4504,9 +4502,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4521,16 +4529,456 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124364664</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>124323891</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Kullvallen, Kullvallen, Hls</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>490832</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6865023</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Ängersjö</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124323891</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>124325068</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Kullvallen, Kullvallen, Hls</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>490832</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6865135</v>
+      </c>
+      <c r="S40" t="n">
+        <v>20</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Ängersjö</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Färsk spillning.</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124325068</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>124364256</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Kullvallen, Kullvallen, Hls</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>490962</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6865124</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Ängersjö</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124364256</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>124364790</v>
+      </c>
+      <c r="B42" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Kullvallen, Kullvallen, Hls</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>491141</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6865216</v>
+      </c>
+      <c r="S42" t="n">
+        <v>15</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Ängersjö</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/124364790</t>
         </is>
@@ -4575,6 +5023,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24249-2024 artfynd.xlsx
+++ b/artfynd/A 24249-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ42"/>
+  <dimension ref="A1:AZ57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,7 +680,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135900796</v>
+        <v>135892133</v>
       </c>
       <c r="B2" t="n">
         <v>79473</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490840</v>
+        <v>490822</v>
       </c>
       <c r="R2" t="n">
-        <v>6865030</v>
+        <v>6864993</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,24 +775,24 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson, Malte Lindberg, Emilia Blixt, Tilde Carlinger</t>
+          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger, Emilia Blixt</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135900796</t>
+          <t>https://artportalen.se/Sighting/135892133</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135900859</v>
+        <v>135900796</v>
       </c>
       <c r="B3" t="n">
         <v>79473</v>
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490779</v>
+        <v>490840</v>
       </c>
       <c r="R3" t="n">
-        <v>6865018</v>
+        <v>6865030</v>
       </c>
       <c r="S3" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,69 +892,60 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson, Tilde Carlinger, Malte Lindberg, Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson, Malte Lindberg, Emilia Blixt, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135900859</t>
+          <t>https://artportalen.se/Sighting/135900796</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124323858</v>
+        <v>135900859</v>
       </c>
       <c r="B4" t="n">
-        <v>92509</v>
+        <v>79473</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>760</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490832</v>
+        <v>490779</v>
       </c>
       <c r="R4" t="n">
-        <v>6865023</v>
+        <v>6865018</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,12 +969,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,65 +999,74 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson, Tilde Carlinger, Malte Lindberg, Emilia Blixt</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124323858</t>
+          <t>https://artportalen.se/Sighting/135900859</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124324393</v>
+        <v>124323858</v>
       </c>
       <c r="B5" t="n">
-        <v>79406</v>
+        <v>92509</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>864</v>
+        <v>760</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490851</v>
+        <v>490832</v>
       </c>
       <c r="R5" t="n">
-        <v>6864963</v>
+        <v>6865023</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1100,27 +1110,27 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124324393</t>
+          <t>https://artportalen.se/Sighting/124323858</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124323707</v>
+        <v>124324393</v>
       </c>
       <c r="B6" t="n">
-        <v>80433</v>
+        <v>79406</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1128,21 +1138,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1152,13 +1162,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490838</v>
+        <v>490851</v>
       </c>
       <c r="R6" t="n">
-        <v>6865007</v>
+        <v>6864963</v>
       </c>
       <c r="S6" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1202,27 +1212,27 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124323707</t>
+          <t>https://artportalen.se/Sighting/124324393</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124324981</v>
+        <v>135892129</v>
       </c>
       <c r="B7" t="n">
-        <v>80433</v>
+        <v>81423</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1230,37 +1240,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>1049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490817</v>
+        <v>490836</v>
       </c>
       <c r="R7" t="n">
-        <v>6865147</v>
+        <v>6865005</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1284,12 +1294,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1304,24 +1324,24 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger, Emilia Blixt</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124324981</t>
+          <t>https://artportalen.se/Sighting/135892129</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124365787</v>
+        <v>124323707</v>
       </c>
       <c r="B8" t="n">
         <v>80433</v>
@@ -1356,13 +1376,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490822</v>
+        <v>490838</v>
       </c>
       <c r="R8" t="n">
-        <v>6865151</v>
+        <v>6865007</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1386,12 +1406,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1417,16 +1437,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124365787</t>
+          <t>https://artportalen.se/Sighting/124323707</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135900799</v>
+        <v>124324981</v>
       </c>
       <c r="B9" t="n">
-        <v>80557</v>
+        <v>80433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,17 +1474,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kullvallen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490843</v>
+        <v>490817</v>
       </c>
       <c r="R9" t="n">
-        <v>6865011</v>
+        <v>6865147</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1488,22 +1508,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>10:10</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>10:10</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1518,69 +1528,65 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson, Malte Lindberg, Emilia Blixt, Tilde Carlinger</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135900799</t>
+          <t>https://artportalen.se/Sighting/124324981</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118676083</v>
+        <v>124365787</v>
       </c>
       <c r="B10" t="n">
-        <v>79327</v>
+        <v>80433</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Öjingsvallen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490841</v>
+        <v>490822</v>
       </c>
       <c r="R10" t="n">
-        <v>6865035</v>
+        <v>6865151</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1604,17 +1610,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1629,65 +1630,65 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118676083</t>
+          <t>https://artportalen.se/Sighting/124365787</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124323575</v>
+        <v>135900799</v>
       </c>
       <c r="B11" t="n">
-        <v>79327</v>
+        <v>80557</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490851</v>
+        <v>490843</v>
       </c>
       <c r="R11" t="n">
-        <v>6865050</v>
+        <v>6865011</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1711,12 +1712,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1731,24 +1742,24 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson, Malte Lindberg, Emilia Blixt, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124323575</t>
+          <t>https://artportalen.se/Sighting/135900799</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124323587</v>
+        <v>118676083</v>
       </c>
       <c r="B12" t="n">
         <v>79327</v>
@@ -1776,20 +1787,24 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Öjingsvallen, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490850</v>
+        <v>490841</v>
       </c>
       <c r="R12" t="n">
-        <v>6865018</v>
+        <v>6865035</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1813,12 +1828,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2024-06-05</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1833,24 +1853,24 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124323587</t>
+          <t>https://artportalen.se/Sighting/118676083</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124323613</v>
+        <v>124323575</v>
       </c>
       <c r="B13" t="n">
         <v>79327</v>
@@ -1885,13 +1905,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490844</v>
+        <v>490851</v>
       </c>
       <c r="R13" t="n">
-        <v>6865014</v>
+        <v>6865050</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1935,24 +1955,24 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124323613</t>
+          <t>https://artportalen.se/Sighting/124323575</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124323622</v>
+        <v>124323587</v>
       </c>
       <c r="B14" t="n">
         <v>79327</v>
@@ -1987,13 +2007,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490832</v>
+        <v>490850</v>
       </c>
       <c r="R14" t="n">
-        <v>6865017</v>
+        <v>6865018</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2037,24 +2057,24 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124323622</t>
+          <t>https://artportalen.se/Sighting/124323587</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124323908</v>
+        <v>124323613</v>
       </c>
       <c r="B15" t="n">
         <v>79327</v>
@@ -2085,17 +2105,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
         <v>490844</v>
       </c>
       <c r="R15" t="n">
-        <v>6864975</v>
+        <v>6865014</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2139,24 +2159,24 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124323908</t>
+          <t>https://artportalen.se/Sighting/124323613</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124324110</v>
+        <v>124323622</v>
       </c>
       <c r="B16" t="n">
         <v>79327</v>
@@ -2187,17 +2207,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490853</v>
+        <v>490832</v>
       </c>
       <c r="R16" t="n">
-        <v>6865011</v>
+        <v>6865017</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2241,24 +2261,24 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124324110</t>
+          <t>https://artportalen.se/Sighting/124323622</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124324167</v>
+        <v>124323908</v>
       </c>
       <c r="B17" t="n">
         <v>79327</v>
@@ -2293,13 +2313,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490860</v>
+        <v>490844</v>
       </c>
       <c r="R17" t="n">
-        <v>6864997</v>
+        <v>6864975</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2343,24 +2363,24 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124324167</t>
+          <t>https://artportalen.se/Sighting/124323908</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124324192</v>
+        <v>124324110</v>
       </c>
       <c r="B18" t="n">
         <v>79327</v>
@@ -2395,10 +2415,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490878</v>
+        <v>490853</v>
       </c>
       <c r="R18" t="n">
-        <v>6864994</v>
+        <v>6865011</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2456,13 +2476,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124324192</t>
+          <t>https://artportalen.se/Sighting/124324110</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124324272</v>
+        <v>124324167</v>
       </c>
       <c r="B19" t="n">
         <v>79327</v>
@@ -2497,10 +2517,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490869</v>
+        <v>490860</v>
       </c>
       <c r="R19" t="n">
-        <v>6864990</v>
+        <v>6864997</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2558,13 +2578,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124324272</t>
+          <t>https://artportalen.se/Sighting/124324167</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124324301</v>
+        <v>124324192</v>
       </c>
       <c r="B20" t="n">
         <v>79327</v>
@@ -2599,13 +2619,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490835</v>
+        <v>490878</v>
       </c>
       <c r="R20" t="n">
-        <v>6864998</v>
+        <v>6864994</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2649,24 +2669,24 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124324301</t>
+          <t>https://artportalen.se/Sighting/124324192</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124324530</v>
+        <v>124324272</v>
       </c>
       <c r="B21" t="n">
         <v>79327</v>
@@ -2701,10 +2721,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490855</v>
+        <v>490869</v>
       </c>
       <c r="R21" t="n">
-        <v>6864955</v>
+        <v>6864990</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2762,13 +2782,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124324530</t>
+          <t>https://artportalen.se/Sighting/124324272</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124324899</v>
+        <v>124324301</v>
       </c>
       <c r="B22" t="n">
         <v>79327</v>
@@ -2803,10 +2823,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490800</v>
+        <v>490835</v>
       </c>
       <c r="R22" t="n">
-        <v>6865161</v>
+        <v>6864998</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2853,24 +2873,24 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124324899</t>
+          <t>https://artportalen.se/Sighting/124324301</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124325022</v>
+        <v>124324530</v>
       </c>
       <c r="B23" t="n">
         <v>79327</v>
@@ -2905,13 +2925,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490825</v>
+        <v>490855</v>
       </c>
       <c r="R23" t="n">
-        <v>6865147</v>
+        <v>6864955</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2966,13 +2986,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124325022</t>
+          <t>https://artportalen.se/Sighting/124324530</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124364496</v>
+        <v>124324899</v>
       </c>
       <c r="B24" t="n">
         <v>79327</v>
@@ -3003,17 +3023,17 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491193</v>
+        <v>490800</v>
       </c>
       <c r="R24" t="n">
-        <v>6865330</v>
+        <v>6865161</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3037,12 +3057,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3057,24 +3077,24 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124364496</t>
+          <t>https://artportalen.se/Sighting/124324899</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124364538</v>
+        <v>124325022</v>
       </c>
       <c r="B25" t="n">
         <v>79327</v>
@@ -3105,17 +3125,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Svartåsen, Svartåsen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491166</v>
+        <v>490825</v>
       </c>
       <c r="R25" t="n">
-        <v>6865362</v>
+        <v>6865147</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3139,12 +3159,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3159,24 +3179,24 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124364538</t>
+          <t>https://artportalen.se/Sighting/124325022</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124364652</v>
+        <v>124364496</v>
       </c>
       <c r="B26" t="n">
         <v>79327</v>
@@ -3211,13 +3231,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>491120</v>
+        <v>491193</v>
       </c>
       <c r="R26" t="n">
-        <v>6865386</v>
+        <v>6865330</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3272,13 +3292,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124364652</t>
+          <t>https://artportalen.se/Sighting/124364496</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124364810</v>
+        <v>124364538</v>
       </c>
       <c r="B27" t="n">
         <v>79327</v>
@@ -3309,14 +3329,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491146</v>
+        <v>491166</v>
       </c>
       <c r="R27" t="n">
-        <v>6865207</v>
+        <v>6865362</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3374,13 +3394,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124364810</t>
+          <t>https://artportalen.se/Sighting/124364538</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124365206</v>
+        <v>124364652</v>
       </c>
       <c r="B28" t="n">
         <v>79327</v>
@@ -3411,17 +3431,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Svartåsen, Svartåsen, Hls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>491179</v>
+        <v>491120</v>
       </c>
       <c r="R28" t="n">
-        <v>6865114</v>
+        <v>6865386</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3476,13 +3496,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124365206</t>
+          <t>https://artportalen.se/Sighting/124364652</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124365478</v>
+        <v>124364810</v>
       </c>
       <c r="B29" t="n">
         <v>79327</v>
@@ -3517,10 +3537,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490807</v>
+        <v>491146</v>
       </c>
       <c r="R29" t="n">
-        <v>6865148</v>
+        <v>6865207</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3578,13 +3598,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124365478</t>
+          <t>https://artportalen.se/Sighting/124364810</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124365822</v>
+        <v>124365206</v>
       </c>
       <c r="B30" t="n">
         <v>79327</v>
@@ -3619,10 +3639,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490796</v>
+        <v>491179</v>
       </c>
       <c r="R30" t="n">
-        <v>6865155</v>
+        <v>6865114</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3680,13 +3700,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124365822</t>
+          <t>https://artportalen.se/Sighting/124365206</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124365903</v>
+        <v>124365478</v>
       </c>
       <c r="B31" t="n">
         <v>79327</v>
@@ -3721,10 +3741,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490934</v>
+        <v>490807</v>
       </c>
       <c r="R31" t="n">
-        <v>6865221</v>
+        <v>6865148</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3754,19 +3774,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>16:02</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>16:02</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3781,24 +3791,24 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124365903</t>
+          <t>https://artportalen.se/Sighting/124365478</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124381335</v>
+        <v>124365822</v>
       </c>
       <c r="B32" t="n">
         <v>79327</v>
@@ -3827,22 +3837,19 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>491025</v>
+        <v>490796</v>
       </c>
       <c r="R32" t="n">
-        <v>6865146</v>
+        <v>6865155</v>
       </c>
       <c r="S32" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3880,56 +3887,55 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124381335</t>
+          <t>https://artportalen.se/Sighting/124365822</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124324335</v>
+        <v>124365903</v>
       </c>
       <c r="B33" t="n">
-        <v>83307</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3939,13 +3945,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490869</v>
+        <v>490934</v>
       </c>
       <c r="R33" t="n">
-        <v>6864990</v>
+        <v>6865221</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3969,12 +3975,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3989,65 +4005,68 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124324335</t>
+          <t>https://artportalen.se/Sighting/124365903</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124323971</v>
+        <v>124381335</v>
       </c>
       <c r="B34" t="n">
-        <v>79084</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Fågelsjö, Hls</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490853</v>
+        <v>491025</v>
       </c>
       <c r="R34" t="n">
-        <v>6865017</v>
+        <v>6865146</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4071,12 +4090,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4085,71 +4104,74 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124323971</t>
+          <t>https://artportalen.se/Sighting/124381335</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124364917</v>
+        <v>135892124</v>
       </c>
       <c r="B35" t="n">
-        <v>79946</v>
+        <v>79441</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>491032</v>
+        <v>490855</v>
       </c>
       <c r="R35" t="n">
-        <v>6865166</v>
+        <v>6865032</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4173,22 +4195,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4197,71 +4219,79 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger, Emilia Blixt</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124364917</t>
+          <t>https://artportalen.se/Sighting/135892124</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124323716</v>
+        <v>135892126</v>
       </c>
       <c r="B36" t="n">
-        <v>80432</v>
+        <v>79441</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490841</v>
+        <v>490845</v>
       </c>
       <c r="R36" t="n">
-        <v>6865011</v>
+        <v>6865022</v>
       </c>
       <c r="S36" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4285,12 +4315,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4299,55 +4339,56 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger, Emilia Blixt</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124323716</t>
+          <t>https://artportalen.se/Sighting/135892126</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135900798</v>
+        <v>135892128</v>
       </c>
       <c r="B37" t="n">
-        <v>80556</v>
+        <v>79441</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4357,13 +4398,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490842</v>
+        <v>490834</v>
       </c>
       <c r="R37" t="n">
-        <v>6865012</v>
+        <v>6865005</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4392,7 +4433,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4402,7 +4443,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4417,65 +4458,65 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson, Malte Lindberg, Emilia Blixt, Tilde Carlinger</t>
+          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger, Emilia Blixt</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135900798</t>
+          <t>https://artportalen.se/Sighting/135892128</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124364664</v>
+        <v>135892134</v>
       </c>
       <c r="B38" t="n">
-        <v>78334</v>
+        <v>79441</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491024</v>
+        <v>490822</v>
       </c>
       <c r="R38" t="n">
-        <v>6865165</v>
+        <v>6864993</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4499,22 +4540,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4529,65 +4570,65 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger, Emilia Blixt</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124364664</t>
+          <t>https://artportalen.se/Sighting/135892134</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124323891</v>
+        <v>135892135</v>
       </c>
       <c r="B39" t="n">
-        <v>57953</v>
+        <v>79441</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490832</v>
+        <v>490820</v>
       </c>
       <c r="R39" t="n">
-        <v>6865023</v>
+        <v>6864990</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4611,17 +4652,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4636,65 +4682,65 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger, Emilia Blixt</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124323891</t>
+          <t>https://artportalen.se/Sighting/135892135</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124325068</v>
+        <v>135892136</v>
       </c>
       <c r="B40" t="n">
-        <v>57141</v>
+        <v>79441</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490832</v>
+        <v>490826</v>
       </c>
       <c r="R40" t="n">
-        <v>6865135</v>
+        <v>6864994</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4718,17 +4764,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Färsk spillning.</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4743,77 +4794,65 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger, Emilia Blixt</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124325068</t>
+          <t>https://artportalen.se/Sighting/135892136</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124364256</v>
+        <v>135892137</v>
       </c>
       <c r="B41" t="n">
-        <v>57141</v>
+        <v>79441</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490962</v>
+        <v>490821</v>
       </c>
       <c r="R41" t="n">
-        <v>6865124</v>
+        <v>6864965</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4837,22 +4876,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4867,27 +4906,27 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger, Emilia Blixt</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124364256</t>
+          <t>https://artportalen.se/Sighting/135892137</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124364790</v>
+        <v>135892130</v>
       </c>
       <c r="B42" t="n">
-        <v>58114</v>
+        <v>78844</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4895,37 +4934,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>6437</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>491141</v>
+        <v>490830</v>
       </c>
       <c r="R42" t="n">
-        <v>6865216</v>
+        <v>6864990</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4949,12 +4988,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4969,18 +5018,1667 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger, Emilia Blixt</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135892130</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>124324335</v>
+      </c>
+      <c r="B43" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Kullvallen, Kullvallen, Hls</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>490869</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6864990</v>
+      </c>
+      <c r="S43" t="n">
+        <v>20</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Ängersjö</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124324335</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135892125</v>
+      </c>
+      <c r="B44" t="n">
+        <v>83428</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Kullvallen, Hls</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>490855</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6865031</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Ängersjö</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger, Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135892125</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>124323971</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Kullvallen, Kullvallen, Hls</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>490853</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6865017</v>
+      </c>
+      <c r="S45" t="n">
+        <v>20</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Ängersjö</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124323971</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>135892197</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79198</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Kullvallen, Hls</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>490797</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6865029</v>
+      </c>
+      <c r="S46" t="n">
+        <v>9</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Ängersjö</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger, Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135892197</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>124364917</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Kullvallen, Kullvallen, Hls</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>491032</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6865166</v>
+      </c>
+      <c r="S47" t="n">
+        <v>15</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Ängersjö</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124364917</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>135892131</v>
+      </c>
+      <c r="B48" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Kullvallen, Hls</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>490830</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6864990</v>
+      </c>
+      <c r="S48" t="n">
+        <v>13</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Ängersjö</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger, Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135892131</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>124323716</v>
+      </c>
+      <c r="B49" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Kullvallen, Kullvallen, Hls</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>490841</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6865011</v>
+      </c>
+      <c r="S49" t="n">
+        <v>12</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Ängersjö</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124323716</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>135900798</v>
+      </c>
+      <c r="B50" t="n">
+        <v>80556</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Kullvallen, Hls</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>490842</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6865012</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Ängersjö</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Nora Toftgård Shahnavaz</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson, Malte Lindberg, Emilia Blixt, Tilde Carlinger</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135900798</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>135892127</v>
+      </c>
+      <c r="B51" t="n">
+        <v>80568</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Kullvallen, Hls</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>490841</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6865014</v>
+      </c>
+      <c r="S51" t="n">
+        <v>17</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Ängersjö</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger, Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135892127</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>124364664</v>
+      </c>
+      <c r="B52" t="n">
+        <v>78334</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Kullvallen, Kullvallen, Hls</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>491024</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6865165</v>
+      </c>
+      <c r="S52" t="n">
+        <v>15</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Ängersjö</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124364664</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>124323891</v>
+      </c>
+      <c r="B53" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Kullvallen, Kullvallen, Hls</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>490832</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6865023</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Ängersjö</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124323891</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>124325068</v>
+      </c>
+      <c r="B54" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Kullvallen, Kullvallen, Hls</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>490832</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6865135</v>
+      </c>
+      <c r="S54" t="n">
+        <v>20</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Ängersjö</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Färsk spillning.</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124325068</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>124364256</v>
+      </c>
+      <c r="B55" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Kullvallen, Kullvallen, Hls</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>490962</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6865124</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Ängersjö</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124364256</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>124364790</v>
+      </c>
+      <c r="B56" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Kullvallen, Kullvallen, Hls</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>491141</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6865216</v>
+      </c>
+      <c r="S56" t="n">
+        <v>15</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Ängersjö</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/124364790</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>135892132</v>
+      </c>
+      <c r="B57" t="n">
+        <v>80031</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Kullvallen, Hls</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>490830</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6864990</v>
+      </c>
+      <c r="S57" t="n">
+        <v>11</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Ängersjö</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger, Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135892132</t>
         </is>
       </c>
     </row>
@@ -5027,6 +6725,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24249-2024 artfynd.xlsx
+++ b/artfynd/A 24249-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135892133</v>
       </c>
       <c r="B2" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135900796</v>
       </c>
       <c r="B3" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135900859</v>
       </c>
       <c r="B4" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>135892129</v>
       </c>
       <c r="B7" t="n">
-        <v>81423</v>
+        <v>81425</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>135900799</v>
       </c>
       <c r="B11" t="n">
-        <v>80557</v>
+        <v>80559</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>135892124</v>
       </c>
       <c r="B35" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4246,7 +4246,7 @@
         <v>135892126</v>
       </c>
       <c r="B36" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
         <v>135892128</v>
       </c>
       <c r="B37" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>135892134</v>
       </c>
       <c r="B38" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>135892135</v>
       </c>
       <c r="B39" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
         <v>135892136</v>
       </c>
       <c r="B40" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>135892137</v>
       </c>
       <c r="B41" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>135892130</v>
       </c>
       <c r="B42" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>135892125</v>
       </c>
       <c r="B44" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>135892197</v>
       </c>
       <c r="B46" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>135892131</v>
       </c>
       <c r="B48" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5795,7 +5795,7 @@
         <v>135900798</v>
       </c>
       <c r="B50" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5907,7 +5907,7 @@
         <v>135892127</v>
       </c>
       <c r="B51" t="n">
-        <v>80568</v>
+        <v>80570</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
         <v>135892132</v>
       </c>
       <c r="B57" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 24249-2024 artfynd.xlsx
+++ b/artfynd/A 24249-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ57"/>
+  <dimension ref="A1:AZ59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4923,48 +4923,51 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135892130</v>
+        <v>135904733</v>
       </c>
       <c r="B42" t="n">
-        <v>78846</v>
+        <v>79443</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490830</v>
+        <v>490802</v>
       </c>
       <c r="R42" t="n">
-        <v>6864990</v>
+        <v>6865029</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4993,7 +4996,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5003,7 +5006,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5012,33 +5015,34 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger, Emilia Blixt</t>
+          <t>Karla Alfaro Gripe, Emilia Blixt, Erik Christiansson, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135892130</t>
+          <t>https://artportalen.se/Sighting/135904733</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124324335</v>
+        <v>135892130</v>
       </c>
       <c r="B43" t="n">
-        <v>83307</v>
+        <v>78846</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5046,31 +5050,31 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>490869</v>
+        <v>490830</v>
       </c>
       <c r="R43" t="n">
         <v>6864990</v>
@@ -5100,12 +5104,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5120,27 +5134,27 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger, Emilia Blixt</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124324335</t>
+          <t>https://artportalen.se/Sighting/135892130</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135892125</v>
+        <v>124324335</v>
       </c>
       <c r="B44" t="n">
-        <v>83430</v>
+        <v>83307</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5166,21 +5180,19 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kullvallen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490855</v>
+        <v>490869</v>
       </c>
       <c r="R44" t="n">
-        <v>6865031</v>
+        <v>6864990</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5204,22 +5216,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>10:10</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>10:10</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5228,34 +5230,33 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger, Emilia Blixt</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135892125</t>
+          <t>https://artportalen.se/Sighting/124324335</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124323971</v>
+        <v>135892125</v>
       </c>
       <c r="B45" t="n">
-        <v>79084</v>
+        <v>83430</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5263,37 +5264,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490853</v>
+        <v>490855</v>
       </c>
       <c r="R45" t="n">
-        <v>6865017</v>
+        <v>6865031</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5317,12 +5320,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5331,33 +5344,34 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger, Emilia Blixt</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124323971</t>
+          <t>https://artportalen.se/Sighting/135892125</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135892197</v>
+        <v>124323971</v>
       </c>
       <c r="B46" t="n">
-        <v>79200</v>
+        <v>79084</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5385,17 +5399,17 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kullvallen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490797</v>
+        <v>490853</v>
       </c>
       <c r="R46" t="n">
-        <v>6865029</v>
+        <v>6865017</v>
       </c>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5419,22 +5433,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>16:18</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>16:18</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5449,27 +5453,27 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger, Emilia Blixt</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135892197</t>
+          <t>https://artportalen.se/Sighting/124323971</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124364917</v>
+        <v>135892197</v>
       </c>
       <c r="B47" t="n">
-        <v>79946</v>
+        <v>79200</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5477,37 +5481,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>491032</v>
+        <v>490797</v>
       </c>
       <c r="R47" t="n">
-        <v>6865166</v>
+        <v>6865029</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5531,22 +5535,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5561,27 +5565,27 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger, Emilia Blixt</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124364917</t>
+          <t>https://artportalen.se/Sighting/135892197</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135892131</v>
+        <v>135904732</v>
       </c>
       <c r="B48" t="n">
-        <v>80062</v>
+        <v>79200</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5589,37 +5593,40 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490830</v>
+        <v>490802</v>
       </c>
       <c r="R48" t="n">
-        <v>6864990</v>
+        <v>6865030</v>
       </c>
       <c r="S48" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5648,7 +5655,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5658,7 +5665,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5667,33 +5674,34 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger, Emilia Blixt</t>
+          <t>Karla Alfaro Gripe, Emilia Blixt, Erik Christiansson, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135892131</t>
+          <t>https://artportalen.se/Sighting/135904732</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124323716</v>
+        <v>124364917</v>
       </c>
       <c r="B49" t="n">
-        <v>80432</v>
+        <v>79946</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5701,21 +5709,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5725,13 +5733,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490841</v>
+        <v>491032</v>
       </c>
       <c r="R49" t="n">
-        <v>6865011</v>
+        <v>6865166</v>
       </c>
       <c r="S49" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5755,12 +5763,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5775,27 +5793,27 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124323716</t>
+          <t>https://artportalen.se/Sighting/124364917</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135900798</v>
+        <v>135892131</v>
       </c>
       <c r="B50" t="n">
-        <v>80558</v>
+        <v>80062</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5803,21 +5821,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5827,13 +5845,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490842</v>
+        <v>490830</v>
       </c>
       <c r="R50" t="n">
-        <v>6865012</v>
+        <v>6864990</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5862,7 +5880,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5872,7 +5890,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5887,68 +5905,65 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson, Malte Lindberg, Emilia Blixt, Tilde Carlinger</t>
+          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger, Emilia Blixt</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135900798</t>
+          <t>https://artportalen.se/Sighting/135892131</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135892127</v>
+        <v>124323716</v>
       </c>
       <c r="B51" t="n">
-        <v>80570</v>
+        <v>80432</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kullvallen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q51" t="n">
         <v>490841</v>
       </c>
       <c r="R51" t="n">
-        <v>6865014</v>
+        <v>6865011</v>
       </c>
       <c r="S51" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5972,22 +5987,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>10:14</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>10:14</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5996,34 +6001,33 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger, Emilia Blixt</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135892127</t>
+          <t>https://artportalen.se/Sighting/124323716</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124364664</v>
+        <v>135900798</v>
       </c>
       <c r="B52" t="n">
-        <v>78334</v>
+        <v>80558</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6031,37 +6035,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6487</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>491024</v>
+        <v>490842</v>
       </c>
       <c r="R52" t="n">
-        <v>6865165</v>
+        <v>6865012</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6085,22 +6089,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6115,65 +6119,68 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson, Malte Lindberg, Emilia Blixt, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124364664</t>
+          <t>https://artportalen.se/Sighting/135900798</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124323891</v>
+        <v>135892127</v>
       </c>
       <c r="B53" t="n">
-        <v>57953</v>
+        <v>80570</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>490832</v>
+        <v>490841</v>
       </c>
       <c r="R53" t="n">
-        <v>6865023</v>
+        <v>6865014</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6197,17 +6204,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6216,55 +6228,56 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger, Emilia Blixt</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124323891</t>
+          <t>https://artportalen.se/Sighting/135892127</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124325068</v>
+        <v>124364664</v>
       </c>
       <c r="B54" t="n">
-        <v>57141</v>
+        <v>78334</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100138</v>
+        <v>6487</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6274,13 +6287,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>490832</v>
+        <v>491024</v>
       </c>
       <c r="R54" t="n">
-        <v>6865135</v>
+        <v>6865165</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6304,17 +6317,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Färsk spillning.</t>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6329,74 +6347,62 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124325068</t>
+          <t>https://artportalen.se/Sighting/124364664</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124364256</v>
+        <v>124323891</v>
       </c>
       <c r="B55" t="n">
-        <v>57141</v>
+        <v>57953</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>490962</v>
+        <v>490832</v>
       </c>
       <c r="R55" t="n">
-        <v>6865124</v>
+        <v>6865023</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6423,22 +6429,17 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>15:16</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>15:16</t>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6453,49 +6454,49 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124364256</t>
+          <t>https://artportalen.se/Sighting/124323891</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124364790</v>
+        <v>124325068</v>
       </c>
       <c r="B56" t="n">
-        <v>58114</v>
+        <v>57141</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6505,13 +6506,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>491141</v>
+        <v>490832</v>
       </c>
       <c r="R56" t="n">
-        <v>6865216</v>
+        <v>6865135</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6535,12 +6536,17 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6555,65 +6561,77 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124364790</t>
+          <t>https://artportalen.se/Sighting/124325068</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135892132</v>
+        <v>124364256</v>
       </c>
       <c r="B57" t="n">
-        <v>80033</v>
+        <v>57141</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kullvallen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>490830</v>
+        <v>490962</v>
       </c>
       <c r="R57" t="n">
-        <v>6864990</v>
+        <v>6865124</v>
       </c>
       <c r="S57" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6637,22 +6655,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6667,16 +6685,230 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger, Emilia Blixt</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124364256</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>124364790</v>
+      </c>
+      <c r="B58" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Kullvallen, Kullvallen, Hls</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>491141</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6865216</v>
+      </c>
+      <c r="S58" t="n">
+        <v>15</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Ängersjö</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124364790</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>135892132</v>
+      </c>
+      <c r="B59" t="n">
+        <v>80033</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Kullvallen, Hls</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>490830</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6864990</v>
+      </c>
+      <c r="S59" t="n">
+        <v>11</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Ängersjö</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger, Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135892132</t>
         </is>
@@ -6740,6 +6972,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24249-2024 artfynd.xlsx
+++ b/artfynd/A 24249-2024 artfynd.xlsx
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124323858</v>
+        <v>136139710</v>
       </c>
       <c r="B5" t="n">
-        <v>92509</v>
+        <v>92638</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,17 +1046,15 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -1066,7 +1064,7 @@
         <v>6865023</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1090,12 +1088,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,24 +1112,45 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Salix caprea</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Emilia Blixt, Nora Toftgård Shahnavaz, Malte Lindberg, Tilde Carlinger, Erik Christiansson, Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124323858</t>
+          <t>https://artportalen.se/Sighting/136139710</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 24249-2024 artfynd.xlsx
+++ b/artfynd/A 24249-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135892133</v>
       </c>
       <c r="B2" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135900796</v>
       </c>
       <c r="B3" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135900859</v>
       </c>
       <c r="B4" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>135892129</v>
       </c>
       <c r="B7" t="n">
-        <v>81425</v>
+        <v>81426</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>135900799</v>
       </c>
       <c r="B11" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>135892124</v>
       </c>
       <c r="B35" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>135892126</v>
       </c>
       <c r="B36" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>135892128</v>
       </c>
       <c r="B37" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4507,7 +4507,7 @@
         <v>135892134</v>
       </c>
       <c r="B38" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>135892135</v>
       </c>
       <c r="B39" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4731,7 +4731,7 @@
         <v>135892136</v>
       </c>
       <c r="B40" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>135892137</v>
       </c>
       <c r="B41" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
         <v>135904733</v>
       </c>
       <c r="B42" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>135892130</v>
       </c>
       <c r="B43" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
         <v>135892125</v>
       </c>
       <c r="B45" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>135892197</v>
       </c>
       <c r="B47" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>135904732</v>
       </c>
       <c r="B48" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>135892131</v>
       </c>
       <c r="B50" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6056,7 +6056,7 @@
         <v>135900798</v>
       </c>
       <c r="B52" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>135892127</v>
       </c>
       <c r="B53" t="n">
-        <v>80570</v>
+        <v>80571</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         <v>135892132</v>
       </c>
       <c r="B59" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 24249-2024 artfynd.xlsx
+++ b/artfynd/A 24249-2024 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>136139710</v>
       </c>
       <c r="B5" t="n">
-        <v>92638</v>
+        <v>92639</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 24249-2024 artfynd.xlsx
+++ b/artfynd/A 24249-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135892133</v>
       </c>
       <c r="B2" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135900796</v>
       </c>
       <c r="B3" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135900859</v>
       </c>
       <c r="B4" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136139710</v>
       </c>
       <c r="B5" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>135892129</v>
       </c>
       <c r="B7" t="n">
-        <v>81426</v>
+        <v>81427</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>135900799</v>
       </c>
       <c r="B11" t="n">
-        <v>80560</v>
+        <v>80561</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>135892124</v>
       </c>
       <c r="B35" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>135892126</v>
       </c>
       <c r="B36" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>135892128</v>
       </c>
       <c r="B37" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4507,7 +4507,7 @@
         <v>135892134</v>
       </c>
       <c r="B38" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>135892135</v>
       </c>
       <c r="B39" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4731,7 +4731,7 @@
         <v>135892136</v>
       </c>
       <c r="B40" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>135892137</v>
       </c>
       <c r="B41" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
         <v>135904733</v>
       </c>
       <c r="B42" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>135892130</v>
       </c>
       <c r="B43" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
         <v>135892125</v>
       </c>
       <c r="B45" t="n">
-        <v>83431</v>
+        <v>83432</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>135892197</v>
       </c>
       <c r="B47" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>135904732</v>
       </c>
       <c r="B48" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>135892131</v>
       </c>
       <c r="B50" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6056,7 +6056,7 @@
         <v>135900798</v>
       </c>
       <c r="B52" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>135892127</v>
       </c>
       <c r="B53" t="n">
-        <v>80571</v>
+        <v>80572</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         <v>135892132</v>
       </c>
       <c r="B59" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 24249-2024 artfynd.xlsx
+++ b/artfynd/A 24249-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135892133</v>
       </c>
       <c r="B2" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135900796</v>
       </c>
       <c r="B3" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135900859</v>
       </c>
       <c r="B4" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136139710</v>
       </c>
       <c r="B5" t="n">
-        <v>92640</v>
+        <v>92646</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>135892129</v>
       </c>
       <c r="B7" t="n">
-        <v>81427</v>
+        <v>81431</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>135900799</v>
       </c>
       <c r="B11" t="n">
-        <v>80561</v>
+        <v>80565</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>135892124</v>
       </c>
       <c r="B35" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>135892126</v>
       </c>
       <c r="B36" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>135892128</v>
       </c>
       <c r="B37" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4507,7 +4507,7 @@
         <v>135892134</v>
       </c>
       <c r="B38" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>135892135</v>
       </c>
       <c r="B39" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4731,7 +4731,7 @@
         <v>135892136</v>
       </c>
       <c r="B40" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>135892137</v>
       </c>
       <c r="B41" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
         <v>135904733</v>
       </c>
       <c r="B42" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>135892130</v>
       </c>
       <c r="B43" t="n">
-        <v>78848</v>
+        <v>78852</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
         <v>135892125</v>
       </c>
       <c r="B45" t="n">
-        <v>83432</v>
+        <v>83436</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>135892197</v>
       </c>
       <c r="B47" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>135904732</v>
       </c>
       <c r="B48" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>135892131</v>
       </c>
       <c r="B50" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6056,7 +6056,7 @@
         <v>135900798</v>
       </c>
       <c r="B52" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>135892127</v>
       </c>
       <c r="B53" t="n">
-        <v>80572</v>
+        <v>80576</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         <v>135892132</v>
       </c>
       <c r="B59" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 24249-2024 artfynd.xlsx
+++ b/artfynd/A 24249-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135892133</v>
       </c>
       <c r="B2" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135900796</v>
       </c>
       <c r="B3" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135900859</v>
       </c>
       <c r="B4" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136139710</v>
       </c>
       <c r="B5" t="n">
-        <v>92646</v>
+        <v>92647</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>135892129</v>
       </c>
       <c r="B7" t="n">
-        <v>81431</v>
+        <v>81432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>135900799</v>
       </c>
       <c r="B11" t="n">
-        <v>80565</v>
+        <v>80566</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>135892124</v>
       </c>
       <c r="B35" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>135892126</v>
       </c>
       <c r="B36" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>135892128</v>
       </c>
       <c r="B37" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4507,7 +4507,7 @@
         <v>135892134</v>
       </c>
       <c r="B38" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>135892135</v>
       </c>
       <c r="B39" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4731,7 +4731,7 @@
         <v>135892136</v>
       </c>
       <c r="B40" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>135892137</v>
       </c>
       <c r="B41" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
         <v>135904733</v>
       </c>
       <c r="B42" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>135892130</v>
       </c>
       <c r="B43" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
         <v>135892125</v>
       </c>
       <c r="B45" t="n">
-        <v>83436</v>
+        <v>83437</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>135892197</v>
       </c>
       <c r="B47" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>135904732</v>
       </c>
       <c r="B48" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>135892131</v>
       </c>
       <c r="B50" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6056,7 +6056,7 @@
         <v>135900798</v>
       </c>
       <c r="B52" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>135892127</v>
       </c>
       <c r="B53" t="n">
-        <v>80576</v>
+        <v>80577</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         <v>135892132</v>
       </c>
       <c r="B59" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 24249-2024 artfynd.xlsx
+++ b/artfynd/A 24249-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135892133</v>
       </c>
       <c r="B2" t="n">
-        <v>79482</v>
+        <v>79486</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135900796</v>
       </c>
       <c r="B3" t="n">
-        <v>79482</v>
+        <v>79486</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135900859</v>
       </c>
       <c r="B4" t="n">
-        <v>79482</v>
+        <v>79486</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136139710</v>
       </c>
       <c r="B5" t="n">
-        <v>92647</v>
+        <v>92653</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>135892129</v>
       </c>
       <c r="B7" t="n">
-        <v>81432</v>
+        <v>81436</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>135900799</v>
       </c>
       <c r="B11" t="n">
-        <v>80566</v>
+        <v>80570</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>135892124</v>
       </c>
       <c r="B35" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>135892126</v>
       </c>
       <c r="B36" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>135892128</v>
       </c>
       <c r="B37" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4507,7 +4507,7 @@
         <v>135892134</v>
       </c>
       <c r="B38" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>135892135</v>
       </c>
       <c r="B39" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4731,7 +4731,7 @@
         <v>135892136</v>
       </c>
       <c r="B40" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>135892137</v>
       </c>
       <c r="B41" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
         <v>135904733</v>
       </c>
       <c r="B42" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>135892130</v>
       </c>
       <c r="B43" t="n">
-        <v>78853</v>
+        <v>78857</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
         <v>135892125</v>
       </c>
       <c r="B45" t="n">
-        <v>83437</v>
+        <v>83441</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>135892197</v>
       </c>
       <c r="B47" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>135904732</v>
       </c>
       <c r="B48" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>135892131</v>
       </c>
       <c r="B50" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6056,7 +6056,7 @@
         <v>135900798</v>
       </c>
       <c r="B52" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>135892127</v>
       </c>
       <c r="B53" t="n">
-        <v>80577</v>
+        <v>80581</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         <v>135892132</v>
       </c>
       <c r="B59" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 24249-2024 artfynd.xlsx
+++ b/artfynd/A 24249-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135892133</v>
       </c>
       <c r="B2" t="n">
-        <v>79486</v>
+        <v>79492</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135900796</v>
       </c>
       <c r="B3" t="n">
-        <v>79486</v>
+        <v>79492</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135900859</v>
       </c>
       <c r="B4" t="n">
-        <v>79486</v>
+        <v>79492</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136139710</v>
       </c>
       <c r="B5" t="n">
-        <v>92653</v>
+        <v>92660</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>135892129</v>
       </c>
       <c r="B7" t="n">
-        <v>81436</v>
+        <v>81442</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>135900799</v>
       </c>
       <c r="B11" t="n">
-        <v>80570</v>
+        <v>80576</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>135892124</v>
       </c>
       <c r="B35" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>135892126</v>
       </c>
       <c r="B36" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>135892128</v>
       </c>
       <c r="B37" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4507,7 +4507,7 @@
         <v>135892134</v>
       </c>
       <c r="B38" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>135892135</v>
       </c>
       <c r="B39" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4731,7 +4731,7 @@
         <v>135892136</v>
       </c>
       <c r="B40" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>135892137</v>
       </c>
       <c r="B41" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
         <v>135904733</v>
       </c>
       <c r="B42" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>135892130</v>
       </c>
       <c r="B43" t="n">
-        <v>78857</v>
+        <v>78863</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
         <v>135892125</v>
       </c>
       <c r="B45" t="n">
-        <v>83441</v>
+        <v>83447</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>135892197</v>
       </c>
       <c r="B47" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>135904732</v>
       </c>
       <c r="B48" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>135892131</v>
       </c>
       <c r="B50" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6056,7 +6056,7 @@
         <v>135900798</v>
       </c>
       <c r="B52" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>135892127</v>
       </c>
       <c r="B53" t="n">
-        <v>80581</v>
+        <v>80587</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         <v>135892132</v>
       </c>
       <c r="B59" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 24249-2024 artfynd.xlsx
+++ b/artfynd/A 24249-2024 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>136139710</v>
       </c>
       <c r="B5" t="n">
-        <v>92660</v>
+        <v>92661</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 24249-2024 artfynd.xlsx
+++ b/artfynd/A 24249-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135892133</v>
       </c>
       <c r="B2" t="n">
-        <v>79492</v>
+        <v>79505</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135900796</v>
       </c>
       <c r="B3" t="n">
-        <v>79492</v>
+        <v>79505</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135900859</v>
       </c>
       <c r="B4" t="n">
-        <v>79492</v>
+        <v>79505</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136139710</v>
       </c>
       <c r="B5" t="n">
-        <v>92661</v>
+        <v>92674</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>135892129</v>
       </c>
       <c r="B7" t="n">
-        <v>81442</v>
+        <v>81455</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>135900799</v>
       </c>
       <c r="B11" t="n">
-        <v>80576</v>
+        <v>80589</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>135892124</v>
       </c>
       <c r="B35" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>135892126</v>
       </c>
       <c r="B36" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>135892128</v>
       </c>
       <c r="B37" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4507,7 +4507,7 @@
         <v>135892134</v>
       </c>
       <c r="B38" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>135892135</v>
       </c>
       <c r="B39" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4731,7 +4731,7 @@
         <v>135892136</v>
       </c>
       <c r="B40" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>135892137</v>
       </c>
       <c r="B41" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
         <v>135904733</v>
       </c>
       <c r="B42" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe, Emilia Blixt, Erik Christiansson, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
+          <t>Karla Alfaro Gripe, Emilia Blixt, Tilde Carlinger, Nora Toftgård Shahnavaz, Malte Lindberg, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5071,7 +5071,7 @@
         <v>135892130</v>
       </c>
       <c r="B43" t="n">
-        <v>78863</v>
+        <v>78876</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
         <v>135892125</v>
       </c>
       <c r="B45" t="n">
-        <v>83447</v>
+        <v>83460</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>135892197</v>
       </c>
       <c r="B47" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>135904732</v>
       </c>
       <c r="B48" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe, Emilia Blixt, Erik Christiansson, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
+          <t>Karla Alfaro Gripe, Emilia Blixt, Tilde Carlinger, Nora Toftgård Shahnavaz, Malte Lindberg, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5842,7 +5842,7 @@
         <v>135892131</v>
       </c>
       <c r="B50" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6056,7 +6056,7 @@
         <v>135900798</v>
       </c>
       <c r="B52" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>135892127</v>
       </c>
       <c r="B53" t="n">
-        <v>80587</v>
+        <v>80600</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         <v>135892132</v>
       </c>
       <c r="B59" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 24249-2024 artfynd.xlsx
+++ b/artfynd/A 24249-2024 artfynd.xlsx
@@ -5056,7 +5056,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe, Emilia Blixt, Tilde Carlinger, Nora Toftgård Shahnavaz, Malte Lindberg, Erik Christiansson</t>
+          <t>Karla Alfaro Gripe, Emilia Blixt, Erik Christiansson, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5715,7 +5715,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe, Emilia Blixt, Tilde Carlinger, Nora Toftgård Shahnavaz, Malte Lindberg, Erik Christiansson</t>
+          <t>Karla Alfaro Gripe, Emilia Blixt, Erik Christiansson, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>

--- a/artfynd/A 24249-2024 artfynd.xlsx
+++ b/artfynd/A 24249-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135892133</v>
       </c>
       <c r="B2" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135900796</v>
       </c>
       <c r="B3" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135900859</v>
       </c>
       <c r="B4" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136139710</v>
       </c>
       <c r="B5" t="n">
-        <v>92674</v>
+        <v>92675</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>135892129</v>
       </c>
       <c r="B7" t="n">
-        <v>81455</v>
+        <v>81456</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>135900799</v>
       </c>
       <c r="B11" t="n">
-        <v>80589</v>
+        <v>80590</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>135892124</v>
       </c>
       <c r="B35" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>135892126</v>
       </c>
       <c r="B36" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>135892128</v>
       </c>
       <c r="B37" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4507,7 +4507,7 @@
         <v>135892134</v>
       </c>
       <c r="B38" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>135892135</v>
       </c>
       <c r="B39" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4731,7 +4731,7 @@
         <v>135892136</v>
       </c>
       <c r="B40" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>135892137</v>
       </c>
       <c r="B41" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
         <v>135904733</v>
       </c>
       <c r="B42" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>135892130</v>
       </c>
       <c r="B43" t="n">
-        <v>78876</v>
+        <v>78877</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
         <v>135892125</v>
       </c>
       <c r="B45" t="n">
-        <v>83460</v>
+        <v>83461</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>135892197</v>
       </c>
       <c r="B47" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>135904732</v>
       </c>
       <c r="B48" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>135892131</v>
       </c>
       <c r="B50" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6056,7 +6056,7 @@
         <v>135900798</v>
       </c>
       <c r="B52" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>135892127</v>
       </c>
       <c r="B53" t="n">
-        <v>80600</v>
+        <v>80601</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         <v>135892132</v>
       </c>
       <c r="B59" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 24249-2024 artfynd.xlsx
+++ b/artfynd/A 24249-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ59"/>
+  <dimension ref="A1:AZ62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5068,32 +5068,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135892130</v>
+        <v>136572862</v>
       </c>
       <c r="B43" t="n">
-        <v>78877</v>
+        <v>79474</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5103,13 +5103,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>490830</v>
+        <v>490832</v>
       </c>
       <c r="R43" t="n">
-        <v>6864990</v>
+        <v>6865014</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5163,65 +5163,65 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger, Emilia Blixt</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135892130</t>
+          <t>https://artportalen.se/Sighting/136572862</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124324335</v>
+        <v>136572863</v>
       </c>
       <c r="B44" t="n">
-        <v>83307</v>
+        <v>79474</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490869</v>
+        <v>490822</v>
       </c>
       <c r="R44" t="n">
-        <v>6864990</v>
+        <v>6864929</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5245,12 +5245,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5265,27 +5275,27 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124324335</t>
+          <t>https://artportalen.se/Sighting/136572863</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135892125</v>
+        <v>135892130</v>
       </c>
       <c r="B45" t="n">
-        <v>83461</v>
+        <v>78877</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5293,39 +5303,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490855</v>
+        <v>490830</v>
       </c>
       <c r="R45" t="n">
-        <v>6865031</v>
+        <v>6864990</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5354,7 +5362,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5364,7 +5372,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5373,7 +5381,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5391,16 +5398,16 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135892125</t>
+          <t>https://artportalen.se/Sighting/135892130</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124323971</v>
+        <v>124324335</v>
       </c>
       <c r="B46" t="n">
-        <v>79084</v>
+        <v>83307</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5408,21 +5415,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5432,10 +5439,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490853</v>
+        <v>490869</v>
       </c>
       <c r="R46" t="n">
-        <v>6865017</v>
+        <v>6864990</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5493,16 +5500,16 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124323971</t>
+          <t>https://artportalen.se/Sighting/124324335</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135892197</v>
+        <v>135892125</v>
       </c>
       <c r="B47" t="n">
-        <v>79231</v>
+        <v>83461</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5510,37 +5517,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490797</v>
+        <v>490855</v>
       </c>
       <c r="R47" t="n">
-        <v>6865029</v>
+        <v>6865031</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5569,7 +5578,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5579,7 +5588,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5588,6 +5597,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5605,16 +5615,16 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135892197</t>
+          <t>https://artportalen.se/Sighting/135892125</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135904732</v>
+        <v>124323971</v>
       </c>
       <c r="B48" t="n">
-        <v>79231</v>
+        <v>79084</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5640,22 +5650,19 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kullvallen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490802</v>
+        <v>490853</v>
       </c>
       <c r="R48" t="n">
-        <v>6865030</v>
+        <v>6865017</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5679,22 +5686,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>16:03</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>16:03</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5703,34 +5700,33 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe, Emilia Blixt, Erik Christiansson, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135904732</t>
+          <t>https://artportalen.se/Sighting/124323971</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124364917</v>
+        <v>135892197</v>
       </c>
       <c r="B49" t="n">
-        <v>79946</v>
+        <v>79231</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5738,37 +5734,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>491032</v>
+        <v>490797</v>
       </c>
       <c r="R49" t="n">
-        <v>6865166</v>
+        <v>6865029</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5792,22 +5788,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5822,27 +5818,27 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger, Emilia Blixt</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124364917</t>
+          <t>https://artportalen.se/Sighting/135892197</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135892131</v>
+        <v>135904732</v>
       </c>
       <c r="B50" t="n">
-        <v>80093</v>
+        <v>79231</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5850,37 +5846,40 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490830</v>
+        <v>490802</v>
       </c>
       <c r="R50" t="n">
-        <v>6864990</v>
+        <v>6865030</v>
       </c>
       <c r="S50" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5909,7 +5908,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5919,7 +5918,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5928,33 +5927,34 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger, Emilia Blixt</t>
+          <t>Karla Alfaro Gripe, Emilia Blixt, Erik Christiansson, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135892131</t>
+          <t>https://artportalen.se/Sighting/135904732</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124323716</v>
+        <v>124364917</v>
       </c>
       <c r="B51" t="n">
-        <v>80432</v>
+        <v>79946</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5962,21 +5962,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5986,13 +5986,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>490841</v>
+        <v>491032</v>
       </c>
       <c r="R51" t="n">
-        <v>6865011</v>
+        <v>6865166</v>
       </c>
       <c r="S51" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6016,12 +6016,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6036,27 +6046,27 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124323716</t>
+          <t>https://artportalen.se/Sighting/124364917</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135900798</v>
+        <v>135892131</v>
       </c>
       <c r="B52" t="n">
-        <v>80589</v>
+        <v>80093</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6064,21 +6074,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6088,13 +6098,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490842</v>
+        <v>490830</v>
       </c>
       <c r="R52" t="n">
-        <v>6865012</v>
+        <v>6864990</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6123,7 +6133,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6133,7 +6143,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6148,68 +6158,65 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson, Malte Lindberg, Emilia Blixt, Tilde Carlinger</t>
+          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger, Emilia Blixt</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135900798</t>
+          <t>https://artportalen.se/Sighting/135892131</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135892127</v>
+        <v>124323716</v>
       </c>
       <c r="B53" t="n">
-        <v>80601</v>
+        <v>80432</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Kullvallen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q53" t="n">
         <v>490841</v>
       </c>
       <c r="R53" t="n">
-        <v>6865014</v>
+        <v>6865011</v>
       </c>
       <c r="S53" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6233,22 +6240,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>10:14</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>10:14</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6257,34 +6254,33 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger, Emilia Blixt</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135892127</t>
+          <t>https://artportalen.se/Sighting/124323716</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124364664</v>
+        <v>135900798</v>
       </c>
       <c r="B54" t="n">
-        <v>78334</v>
+        <v>80589</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6292,37 +6288,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6487</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>491024</v>
+        <v>490842</v>
       </c>
       <c r="R54" t="n">
-        <v>6865165</v>
+        <v>6865012</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6346,22 +6342,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6376,65 +6372,68 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson, Malte Lindberg, Emilia Blixt, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124364664</t>
+          <t>https://artportalen.se/Sighting/135900798</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124323891</v>
+        <v>135892127</v>
       </c>
       <c r="B55" t="n">
-        <v>57953</v>
+        <v>80601</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kullvallen, Kullvallen, Hls</t>
+          <t>Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>490832</v>
+        <v>490841</v>
       </c>
       <c r="R55" t="n">
-        <v>6865023</v>
+        <v>6865014</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6458,17 +6457,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6477,55 +6481,56 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger, Emilia Blixt</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124323891</t>
+          <t>https://artportalen.se/Sighting/135892127</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124325068</v>
+        <v>124364664</v>
       </c>
       <c r="B56" t="n">
-        <v>57141</v>
+        <v>78334</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100138</v>
+        <v>6487</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6535,13 +6540,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490832</v>
+        <v>491024</v>
       </c>
       <c r="R56" t="n">
-        <v>6865135</v>
+        <v>6865165</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6565,17 +6570,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Färsk spillning.</t>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6590,74 +6600,62 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124325068</t>
+          <t>https://artportalen.se/Sighting/124364664</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124364256</v>
+        <v>124323891</v>
       </c>
       <c r="B57" t="n">
-        <v>57141</v>
+        <v>57953</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>490962</v>
+        <v>490832</v>
       </c>
       <c r="R57" t="n">
-        <v>6865124</v>
+        <v>6865023</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6684,22 +6682,17 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>15:16</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>15:16</t>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6714,49 +6707,49 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124364256</t>
+          <t>https://artportalen.se/Sighting/124323891</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124364790</v>
+        <v>124325068</v>
       </c>
       <c r="B58" t="n">
-        <v>58114</v>
+        <v>57141</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6766,13 +6759,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>491141</v>
+        <v>490832</v>
       </c>
       <c r="R58" t="n">
-        <v>6865216</v>
+        <v>6865135</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6796,12 +6789,17 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6816,65 +6814,77 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124364790</t>
+          <t>https://artportalen.se/Sighting/124325068</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135892132</v>
+        <v>124364256</v>
       </c>
       <c r="B59" t="n">
-        <v>80064</v>
+        <v>57141</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Kullvallen, Hls</t>
+          <t>Kullvallen, Kullvallen, Hls</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490830</v>
+        <v>490962</v>
       </c>
       <c r="R59" t="n">
-        <v>6864990</v>
+        <v>6865124</v>
       </c>
       <c r="S59" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6898,22 +6908,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6928,16 +6938,342 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger, Emilia Blixt</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124364256</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>124364790</v>
+      </c>
+      <c r="B60" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Kullvallen, Kullvallen, Hls</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>491141</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6865216</v>
+      </c>
+      <c r="S60" t="n">
+        <v>15</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Ängersjö</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124364790</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>136572893</v>
+      </c>
+      <c r="B61" t="n">
+        <v>58870</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Kullvallen, Hls</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>490742</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6865068</v>
+      </c>
+      <c r="S61" t="n">
+        <v>22</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Ängersjö</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Tilde Carlinger</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Tilde Carlinger</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136572893</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>135892132</v>
+      </c>
+      <c r="B62" t="n">
+        <v>80064</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Kullvallen, Hls</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>490830</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6864990</v>
+      </c>
+      <c r="S62" t="n">
+        <v>11</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Ängersjö</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger, Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135892132</t>
         </is>
@@ -7003,6 +7339,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
